--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>WFRD</t>
   </si>
@@ -656,264 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1362000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1313000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1274000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1186000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1209000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1120000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1064000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>938000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>965000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>945000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>903000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>832000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>842000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>807000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>821000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1215000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1246000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E9" s="3">
         <v>859000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>847000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>790000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>807000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>775000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>756000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>682000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>717000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>686000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>677000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>636000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>654000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>631000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>609000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>913000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>953000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>463000</v>
+      </c>
+      <c r="E10" s="3">
         <v>454000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>427000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>396000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>402000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>345000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>308000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>256000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>248000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>259000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>226000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>196000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>188000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>176000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>212000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>302000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>293000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,37 +946,38 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E12" s="3">
         <v>30000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>21000</v>
       </c>
       <c r="M12" s="3">
         <v>21000</v>
@@ -973,25 +986,28 @@
         <v>21000</v>
       </c>
       <c r="O12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="P12" s="3">
         <v>20000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>33000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>36000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1046,81 +1062,87 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-5000</v>
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>9000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-14000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>39000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>117000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>51000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-8000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>137000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>31000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>441000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>852000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E15" s="3">
         <v>37000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>40000</v>
       </c>
       <c r="F15" s="3">
         <v>40000</v>
       </c>
       <c r="G15" s="3">
+        <v>40000</v>
+      </c>
+      <c r="H15" s="3">
         <v>38000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>39000</v>
       </c>
       <c r="I15" s="3">
         <v>39000</v>
@@ -1140,8 +1162,8 @@
       <c r="N15" s="3">
         <v>39000</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>11</v>
+      <c r="O15" s="3">
+        <v>39000</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>11</v>
@@ -1158,8 +1180,11 @@
       <c r="T15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1151000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1095000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1073000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1001000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1043000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1001000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>960000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>920000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1043000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>933000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>878000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>845000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>949000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>867000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1318000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2046000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E18" s="3">
         <v>218000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>201000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>185000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>166000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>119000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>104000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-78000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-107000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-497000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-831000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5373000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,120 +1343,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-54000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-127000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-66000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-69000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-56000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-80000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-64000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-59000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-73000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-83000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-74000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-67000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-99000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-70000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-83000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-41000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>232000</v>
+      </c>
+      <c r="E21" s="3">
         <v>247000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>155000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>199000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>181000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>151000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>114000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>41000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>51000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-58000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-454000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-757000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5456000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1479,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E23" s="3">
         <v>164000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>74000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>119000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>97000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>63000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-137000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-61000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-58000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-87000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-174000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-567000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-914000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5332000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>33000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>38000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>44000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>68000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E26" s="3">
         <v>131000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>90000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>81000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>76000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-74000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-157000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-89000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-73000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-195000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-167000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-579000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-958000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5264000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E27" s="3">
         <v>123000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>82000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>72000</v>
       </c>
       <c r="G27" s="3">
         <v>72000</v>
       </c>
       <c r="H27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I27" s="3">
         <v>28000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-80000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-161000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-95000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-78000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-116000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-581000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-966000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5253000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E32" s="3">
         <v>54000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>127000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>66000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>69000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>56000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>80000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>64000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>59000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>73000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>83000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>74000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>67000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>99000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>70000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>83000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>41000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E33" s="3">
         <v>123000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>82000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>72000</v>
       </c>
       <c r="G33" s="3">
         <v>72000</v>
       </c>
       <c r="H33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I33" s="3">
         <v>28000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-80000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-161000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-95000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-78000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-116000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-581000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-966000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5253000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E35" s="3">
         <v>123000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>82000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>72000</v>
       </c>
       <c r="G35" s="3">
         <v>72000</v>
       </c>
       <c r="H35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I35" s="3">
         <v>28000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-80000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-161000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-95000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-78000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-116000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-581000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-966000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5253000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>958000</v>
+      </c>
+      <c r="E41" s="3">
         <v>839000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>787000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>833000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>910000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>933000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>879000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>841000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>951000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1291000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1217000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1177000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1118000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>680000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>670000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>618000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,246 +2513,261 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1277000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1318000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1120000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1123000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1028000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>927000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>930000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>868000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>825000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>816000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>782000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>793000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>833000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>836000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>929000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1206000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1244000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>788000</v>
+      </c>
+      <c r="E44" s="3">
         <v>776000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>751000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>719000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>689000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>723000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>716000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>684000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>670000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>681000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>662000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>676000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>717000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>811000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>862000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1004000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>972000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E45" s="3">
         <v>287000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>313000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>368000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>416000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>480000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>485000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>496000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>465000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>456000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>465000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>512000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>509000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>525000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>456000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>494000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>619000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3345000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3220000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="F46" s="3">
-        <v>3043000</v>
       </c>
       <c r="G46" s="3">
         <v>3043000</v>
       </c>
       <c r="H46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="I46" s="3">
         <v>3063000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3010000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2889000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2911000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3244000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3126000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3158000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3177000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3293000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2927000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3374000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3453000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E47" s="3">
         <v>28000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25000</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>11</v>
@@ -2680,8 +2784,8 @@
       <c r="L47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2704,120 +2808,129 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1054000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1033000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1049000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1033000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1019000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1054000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1083000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1109000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1139000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1234000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1298000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1374000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1451000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1522000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1726000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2378000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E49" s="3">
         <v>404000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>440000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>474000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>506000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>540000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>579000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>619000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>657000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>695000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>734000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>771000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>810000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>841000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>875000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1000000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1353000</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E52" s="3">
         <v>189000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>177000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>118000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>138000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>85000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>92000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>93000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>97000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>70000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>66000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>68000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>73000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>79000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>85000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>65000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>109000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5068000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4895000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4648000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4709000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4720000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4707000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4735000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4684000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4774000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5148000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5160000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5295000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5434000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5664000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5409000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6165000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7293000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,344 +3269,363 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>679000</v>
+      </c>
+      <c r="E57" s="3">
         <v>620000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>502000</v>
       </c>
       <c r="F57" s="3">
         <v>502000</v>
       </c>
       <c r="G57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="H57" s="3">
         <v>460000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>425000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>448000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>385000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>380000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>350000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>348000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>330000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>325000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>332000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>384000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>544000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>585000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E58" s="3">
         <v>91000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>120000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>64000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>211000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>26000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1020000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>929000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>889000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>965000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>945000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>871000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>902000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>940000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>963000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>885000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1023000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1024000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1070000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1074000</v>
       </c>
       <c r="S59" s="3">
         <v>1074000</v>
       </c>
       <c r="T59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="U59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1866000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1731000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1464000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1511000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1470000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1384000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1383000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1332000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1524000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1243000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1364000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1362000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1416000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1426000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1644000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1672000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1715000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1864000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1993000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2067000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2366000</v>
       </c>
       <c r="I61" s="3">
         <v>2366000</v>
       </c>
       <c r="J61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="K61" s="3">
         <v>2416000</v>
       </c>
       <c r="L61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="M61" s="3">
         <v>2431000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2605000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2602000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2601000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2602000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2148000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2149000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2151000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E62" s="3">
         <v>537000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>519000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>545000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>496000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>485000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>495000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>542000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>530000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>546000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>553000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>508000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>534000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>523000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>530000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>509000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>554000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4144000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4153000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4003000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4142000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4185000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4254000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4269000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4288000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4302000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4527000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4434000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4508000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4527000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4577000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4142000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4346000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4413000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1954000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-992000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-26000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>924000</v>
+      </c>
+      <c r="E76" s="3">
         <v>742000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>645000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>567000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>535000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>453000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>466000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>396000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>472000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>621000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>726000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>787000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>907000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1087000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1267000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1819000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2880000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E81" s="3">
         <v>123000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>82000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>72000</v>
       </c>
       <c r="G81" s="3">
         <v>72000</v>
       </c>
       <c r="H81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I81" s="3">
         <v>28000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-80000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-161000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-95000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-78000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-116000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-581000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-966000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5253000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4430,55 +4628,58 @@
         <v>83000</v>
       </c>
       <c r="E83" s="3">
+        <v>83000</v>
+      </c>
+      <c r="F83" s="3">
         <v>81000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>80000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>84000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>88000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>90000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>87000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>103000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>112000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>114000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>111000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>116000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>117000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>113000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>157000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>124000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E89" s="3">
         <v>172000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>201000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>84000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>193000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>160000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-64000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>88000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>114000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>74000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>127000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-42000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-39000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-54000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-35000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-93000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-58000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-32000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-81000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>21000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-75000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-126000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-91000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-170000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-127000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-159000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-64000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-338000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-50000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-52000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>412000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-170000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-34000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-33000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E102" s="3">
         <v>24000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-61000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-129000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-31000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>53000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-333000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>59000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>44000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>58000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>537000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-250000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>WFRD</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1362000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1313000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1274000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1186000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1209000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1120000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1064000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>938000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>965000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>945000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>903000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>832000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>842000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>807000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>821000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1215000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1246000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E9" s="3">
         <v>899000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>859000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>847000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>790000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>807000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>775000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>756000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>682000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>717000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>686000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>677000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>636000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>654000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>631000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>609000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>913000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>953000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E10" s="3">
         <v>463000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>454000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>427000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>396000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>402000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>345000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>308000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>256000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>248000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>259000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>226000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>196000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>188000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>176000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>212000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>302000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>293000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,40 +960,41 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E12" s="3">
         <v>29000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>21000</v>
       </c>
       <c r="N12" s="3">
         <v>21000</v>
@@ -989,25 +1003,28 @@
         <v>21000</v>
       </c>
       <c r="P12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Q12" s="3">
         <v>20000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>21000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>33000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>36000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,87 +1082,93 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3">
         <v>5000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>9000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>39000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>117000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>51000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-8000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>137000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>31000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>441000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>852000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E15" s="3">
         <v>39000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>37000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40000</v>
       </c>
       <c r="G15" s="3">
         <v>40000</v>
       </c>
       <c r="H15" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I15" s="3">
         <v>38000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>39000</v>
       </c>
       <c r="J15" s="3">
         <v>39000</v>
@@ -1165,8 +1188,8 @@
       <c r="O15" s="3">
         <v>39000</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>11</v>
+      <c r="P15" s="3">
+        <v>39000</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>11</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1125000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1151000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1095000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1073000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1001000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1043000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1001000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>960000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>920000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1043000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>933000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>878000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>845000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>949000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>867000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1318000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2046000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E18" s="3">
         <v>211000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>218000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>201000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>185000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>166000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>119000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>104000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-78000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-60000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-497000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-831000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5373000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,126 +1377,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-62000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-54000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-127000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-66000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-69000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-56000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-80000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-64000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-59000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-73000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-83000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-74000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-99000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-70000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-83000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-41000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E21" s="3">
         <v>232000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>247000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>155000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>199000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>181000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>151000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>114000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>41000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>51000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>56000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-42000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-454000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-757000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5456000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,126 +1561,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E23" s="3">
         <v>149000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>164000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>74000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>119000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>97000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>63000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-137000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-61000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-58000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-87000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-159000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-567000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-914000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5332000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>33000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-16000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>38000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>68000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E26" s="3">
         <v>147000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>131000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>90000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>81000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>37000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-74000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-157000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-89000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-73000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-110000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-195000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-167000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-579000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-958000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5264000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>140000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>123000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>82000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>72000</v>
       </c>
       <c r="H27" s="3">
         <v>72000</v>
       </c>
       <c r="I27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J27" s="3">
         <v>28000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-80000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-161000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-95000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-78000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-116000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-174000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-581000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-966000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5253000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E32" s="3">
         <v>62000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>54000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>127000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>66000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>69000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>56000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>80000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>64000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>59000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>73000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>83000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>74000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>67000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>99000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>70000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>83000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>41000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>140000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>123000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>82000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>72000</v>
       </c>
       <c r="H33" s="3">
         <v>72000</v>
       </c>
       <c r="I33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J33" s="3">
         <v>28000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-80000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-161000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-95000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-78000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-116000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-174000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-581000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-966000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5253000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>140000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>123000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>82000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>72000</v>
       </c>
       <c r="H35" s="3">
         <v>72000</v>
       </c>
       <c r="I35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J35" s="3">
         <v>28000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-80000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-161000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-95000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-78000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-116000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-174000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-581000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-966000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5253000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2484,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E41" s="3">
         <v>958000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>839000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>787000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>833000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>910000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>933000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>879000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>841000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>951000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1291000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1217000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1177000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1118000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1121000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>680000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>670000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>618000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,261 +2606,276 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1303000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1277000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1318000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1120000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1123000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1028000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>927000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>930000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>868000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>825000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>816000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>782000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>793000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>833000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>836000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>929000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1206000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1244000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>850000</v>
+      </c>
+      <c r="E44" s="3">
         <v>788000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>776000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>751000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>719000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>689000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>723000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>716000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>684000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>670000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>681000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>662000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>676000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>717000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>811000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>862000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1004000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>972000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E45" s="3">
         <v>322000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>287000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>313000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>368000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>416000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>480000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>485000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>496000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>465000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>456000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>465000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>512000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>509000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>525000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>456000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>494000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>619000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3312000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3345000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3220000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>3043000</v>
       </c>
       <c r="H46" s="3">
         <v>3043000</v>
       </c>
       <c r="I46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="J46" s="3">
         <v>3063000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3010000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2889000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2911000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3244000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3126000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3158000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3177000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3293000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2927000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3374000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3453000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E47" s="3">
         <v>24000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>25000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>11</v>
@@ -2787,8 +2892,8 @@
       <c r="M47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2811,126 +2916,135 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1095000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1054000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1033000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1049000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1033000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1019000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1054000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1083000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1109000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1139000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1234000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1298000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1374000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1451000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1522000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1726000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2378000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E49" s="3">
         <v>370000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>404000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>440000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>474000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>506000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>540000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>579000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>619000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>657000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>695000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>734000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>771000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>810000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>841000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>875000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1000000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1353000</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,67 +3164,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E52" s="3">
         <v>234000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>189000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>177000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>118000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>138000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>85000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>92000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>93000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>97000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>70000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>68000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>73000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>79000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>85000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>65000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>109000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5090000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5068000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4895000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4648000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4709000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4720000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4707000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4735000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4684000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4774000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5148000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5160000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5295000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5434000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5664000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5409000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6165000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7293000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,362 +3400,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E57" s="3">
         <v>679000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>620000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>502000</v>
       </c>
       <c r="G57" s="3">
         <v>502000</v>
       </c>
       <c r="H57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="I57" s="3">
         <v>460000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>425000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>448000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>385000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>380000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>350000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>348000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>330000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>325000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>332000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>384000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>544000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>585000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E58" s="3">
         <v>168000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>91000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>120000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>45000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>64000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>211000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>983000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1019000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1020000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>929000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>889000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>965000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>945000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>871000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>902000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>940000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>963000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>885000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1023000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1024000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1070000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1074000</v>
       </c>
       <c r="T59" s="3">
         <v>1074000</v>
       </c>
       <c r="U59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="V59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1866000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1731000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1464000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1511000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1470000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1384000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1383000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1300000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1332000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1524000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1243000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1364000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1362000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1416000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1426000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1644000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1672000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1629000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1715000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1864000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1993000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2067000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2366000</v>
       </c>
       <c r="J61" s="3">
         <v>2366000</v>
       </c>
       <c r="K61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="L61" s="3">
         <v>2416000</v>
       </c>
       <c r="M61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2431000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2605000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2602000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2601000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2602000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2148000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2149000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2151000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E62" s="3">
         <v>565000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>537000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>519000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>545000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>496000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>485000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>495000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>542000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>530000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>546000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>553000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>508000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>534000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>523000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>530000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>509000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>554000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3999000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4144000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4153000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4003000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4142000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4185000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4254000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4269000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4288000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4302000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4527000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4434000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4508000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4527000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4577000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4142000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4346000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4413000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1842000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-992000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-26000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E76" s="3">
         <v>924000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>742000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>645000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>567000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>535000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>453000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>466000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>396000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>472000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>621000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>726000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>787000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>907000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1087000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1267000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1819000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2880000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>140000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>123000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>82000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>72000</v>
       </c>
       <c r="H81" s="3">
         <v>72000</v>
       </c>
       <c r="I81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J81" s="3">
         <v>28000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-80000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-161000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-95000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-78000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-116000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-174000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-581000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-966000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5253000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,67 +4817,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>83000</v>
+        <v>85000</v>
       </c>
       <c r="E83" s="3">
         <v>83000</v>
       </c>
       <c r="F83" s="3">
+        <v>83000</v>
+      </c>
+      <c r="G83" s="3">
         <v>81000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>80000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>84000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>88000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>90000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>87000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>103000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>112000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>114000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>111000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>116000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>117000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>113000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>157000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>124000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E89" s="3">
         <v>375000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>172000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>201000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>84000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>193000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>160000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>60000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-64000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>114000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>74000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>127000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>30000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-67000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-42000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-64000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-49000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-35000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-38000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-93000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-131000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-36000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-58000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-32000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-81000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>1000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>21000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-51000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-75000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +5793,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-187000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-126000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-91000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-170000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-127000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-159000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-64000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-338000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-50000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>412000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-170000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-34000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-33000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-11000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-126000</v>
+      </c>
+      <c r="E102" s="3">
         <v>117000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-61000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-129000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-31000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>53000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>34000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-57000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-333000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>59000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>44000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>58000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>537000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-36000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-250000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>WFRD</t>
   </si>
@@ -656,289 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1405000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1358000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1362000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1313000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1274000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1186000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1209000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1120000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1064000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>938000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>965000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>945000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>903000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>832000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>842000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>807000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>821000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1215000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1246000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E9" s="3">
         <v>884000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>899000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>859000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>847000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>790000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>807000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>775000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>756000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>682000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>717000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>686000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>677000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>636000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>654000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>631000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>609000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>913000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>953000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E10" s="3">
         <v>474000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>463000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>454000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>427000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>396000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>402000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>345000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>308000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>256000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>248000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>259000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>226000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>196000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>188000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>176000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>212000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>302000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>293000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,34 +984,34 @@
         <v>31000</v>
       </c>
       <c r="E12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F12" s="3">
         <v>29000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>21000</v>
       </c>
       <c r="O12" s="3">
         <v>21000</v>
@@ -1006,25 +1020,28 @@
         <v>21000</v>
       </c>
       <c r="Q12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="R12" s="3">
         <v>20000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>33000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>36000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,70 +1102,76 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3">
         <v>5000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>9000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>39000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>117000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>51000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-8000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>137000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>31000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>441000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>852000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1156,22 +1179,22 @@
         <v>41000</v>
       </c>
       <c r="E15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F15" s="3">
         <v>39000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>37000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>40000</v>
       </c>
       <c r="H15" s="3">
         <v>40000</v>
       </c>
       <c r="I15" s="3">
+        <v>40000</v>
+      </c>
+      <c r="J15" s="3">
         <v>38000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>39000</v>
       </c>
       <c r="K15" s="3">
         <v>39000</v>
@@ -1191,8 +1214,8 @@
       <c r="P15" s="3">
         <v>39000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>11</v>
+      <c r="Q15" s="3">
+        <v>39000</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>11</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1141000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1125000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1151000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1095000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1073000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1001000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1043000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1001000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>960000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>920000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1043000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>933000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>878000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>845000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>949000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>867000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1318000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2046000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E18" s="3">
         <v>233000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>211000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>218000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>201000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>185000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>166000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>119000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>104000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-78000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-107000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-60000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-497000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-831000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5373000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,132 +1411,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-51000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-62000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-54000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-127000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-66000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-69000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-56000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-80000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-64000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-59000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-73000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-83000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-67000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-99000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-70000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-83000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-41000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E21" s="3">
         <v>267000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>232000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>247000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>155000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>199000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>181000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>151000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>114000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>41000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>51000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>56000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-58000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-42000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-454000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-757000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5456000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1564,132 +1604,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E23" s="3">
         <v>182000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>149000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>164000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>74000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>119000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>97000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>63000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-137000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-61000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-58000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-87000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-174000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-159000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-567000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-914000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5332000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E24" s="3">
         <v>59000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>44000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>68000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E26" s="3">
         <v>123000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>147000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>131000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>90000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>81000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>37000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-74000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-157000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-89000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-73000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-110000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-195000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-167000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-579000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-958000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5264000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E27" s="3">
         <v>112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>140000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>123000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>82000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>72000</v>
       </c>
       <c r="I27" s="3">
         <v>72000</v>
       </c>
       <c r="J27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K27" s="3">
         <v>28000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-80000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-161000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-95000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-78000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-174000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-581000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-966000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5253000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2189,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E32" s="3">
         <v>51000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>62000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>54000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>127000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>66000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>69000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>56000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>80000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>64000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>59000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>73000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>83000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>74000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>67000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>99000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>70000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>83000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>41000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E33" s="3">
         <v>112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>140000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>123000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>82000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>72000</v>
       </c>
       <c r="I33" s="3">
         <v>72000</v>
       </c>
       <c r="J33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K33" s="3">
         <v>28000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-80000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-161000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-95000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-78000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-174000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-581000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-966000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5253000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E35" s="3">
         <v>112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>140000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>123000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>82000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>72000</v>
       </c>
       <c r="I35" s="3">
         <v>72000</v>
       </c>
       <c r="J35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K35" s="3">
         <v>28000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-80000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-161000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-95000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-78000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-174000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-581000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-966000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5253000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,70 +2571,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>862000</v>
+      </c>
+      <c r="E41" s="3">
         <v>824000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>958000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>839000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>787000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>833000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>910000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>933000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>879000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>841000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>951000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1291000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1217000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1177000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1118000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1121000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>680000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>670000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>618000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,276 +2699,291 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1372000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1303000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1277000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1318000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1120000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1123000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1028000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>927000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>930000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>868000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>825000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>816000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>782000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>793000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>833000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>836000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>929000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1206000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1244000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E44" s="3">
         <v>850000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>788000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>776000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>751000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>719000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>689000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>723000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>716000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>684000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>670000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>681000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>662000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>676000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>717000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>811000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>862000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1004000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>972000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E45" s="3">
         <v>335000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>322000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>287000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>313000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>368000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>416000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>480000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>485000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>496000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>465000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>456000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>465000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>512000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>509000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>525000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>456000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>494000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>619000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3362000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3312000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3345000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3220000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>3043000</v>
       </c>
       <c r="I46" s="3">
         <v>3043000</v>
       </c>
       <c r="J46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="K46" s="3">
         <v>3063000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3010000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2889000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2911000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3244000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3126000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3158000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3177000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3293000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2927000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3374000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3453000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E47" s="3">
         <v>26000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>25000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>11</v>
@@ -2895,8 +3000,8 @@
       <c r="N47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2919,132 +3024,141 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1123000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1095000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1054000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1033000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1049000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1033000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1019000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1054000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1083000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1109000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1139000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1234000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1374000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1451000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1522000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1726000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2378000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E49" s="3">
         <v>417000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>370000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>404000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>440000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>474000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>506000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>540000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>579000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>619000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>657000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>695000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>734000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>771000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>810000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>841000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>875000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1000000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1353000</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,70 +3284,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E52" s="3">
         <v>212000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>234000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>189000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>177000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>118000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>138000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>85000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>92000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>93000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>97000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>70000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>68000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>73000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>79000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>85000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>65000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>109000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5111000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5090000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5068000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4895000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4648000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4709000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4720000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4707000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4735000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4684000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4774000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5148000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5160000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5295000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5434000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5664000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5409000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6165000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7293000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,380 +3531,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>771000</v>
+      </c>
+      <c r="E57" s="3">
         <v>716000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>679000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>620000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>502000</v>
       </c>
       <c r="H57" s="3">
         <v>502000</v>
       </c>
       <c r="I57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="J57" s="3">
         <v>460000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>425000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>448000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>385000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>380000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>350000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>348000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>330000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>325000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>332000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>384000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>544000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>585000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E58" s="3">
         <v>101000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>168000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>91000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>33000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>120000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>64000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>211000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900000</v>
+      </c>
+      <c r="E59" s="3">
         <v>983000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1019000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1020000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>929000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>889000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>965000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>945000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>871000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>902000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>940000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>963000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>885000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1023000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1024000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1070000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1074000</v>
       </c>
       <c r="U59" s="3">
         <v>1074000</v>
       </c>
       <c r="V59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="W59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1691000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1800000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1866000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1731000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1464000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1511000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1470000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1384000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1383000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1300000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1332000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1524000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1243000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1364000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1362000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1416000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1426000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1644000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1672000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1628000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1629000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1715000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1864000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1993000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2067000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2366000</v>
       </c>
       <c r="K61" s="3">
         <v>2366000</v>
       </c>
       <c r="L61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="M61" s="3">
         <v>2416000</v>
       </c>
       <c r="N61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="O61" s="3">
         <v>2431000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2605000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2602000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2601000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2602000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2148000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2149000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2151000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E62" s="3">
         <v>561000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>565000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>537000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>519000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>545000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>496000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>485000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>495000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>542000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>530000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>546000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>553000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>508000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>534000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>523000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>530000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>509000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>554000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3883000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3999000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4144000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4153000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4003000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4142000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4185000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4254000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4269000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4288000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4302000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4527000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4434000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4508000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4527000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4577000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4142000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4346000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4413000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1717000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-992000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-26000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1228000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1091000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>924000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>742000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>645000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>567000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>535000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>453000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>466000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>396000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>472000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>621000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>726000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>787000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>907000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1087000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1267000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1819000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2880000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E81" s="3">
         <v>112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>140000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>123000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>82000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>72000</v>
       </c>
       <c r="I81" s="3">
         <v>72000</v>
       </c>
       <c r="J81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K81" s="3">
         <v>28000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-80000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-161000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-95000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-78000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-174000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-581000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-966000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5253000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5016,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E83" s="3">
         <v>85000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>83000</v>
       </c>
       <c r="F83" s="3">
         <v>83000</v>
       </c>
       <c r="G83" s="3">
+        <v>83000</v>
+      </c>
+      <c r="H83" s="3">
         <v>81000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>80000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>84000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>88000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>90000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>87000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>103000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>112000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>114000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>111000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>116000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>117000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>113000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>157000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>124000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E89" s="3">
         <v>131000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>375000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>172000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>201000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>84000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>193000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>160000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>60000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-64000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>114000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>46000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>74000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>127000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5496,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-59000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-67000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-49000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-54000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-35000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-38000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-93000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-54000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-131000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-36000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-58000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-32000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-81000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>1000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>21000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-51000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-75000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,190 +6039,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-187000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-126000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-91000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-170000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-127000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-159000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-64000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-338000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-50000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-52000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>412000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-170000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-16000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-21000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-22000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-33000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-11000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-126000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>117000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-61000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-129000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-57000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-333000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>59000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>58000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>537000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-36000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-250000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>WFRD</t>
   </si>
@@ -656,302 +656,315 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1409000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1405000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1358000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1362000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1313000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1274000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1186000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1209000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1120000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1064000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>938000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>965000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>945000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>903000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>832000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>842000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>807000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>821000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1215000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1246000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>917000</v>
+      </c>
+      <c r="E9" s="3">
         <v>891000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>884000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>899000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>859000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>847000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>790000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>807000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>775000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>756000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>682000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>717000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>686000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>677000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>636000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>654000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>631000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>609000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>913000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>953000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E10" s="3">
         <v>514000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>474000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>463000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>454000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>427000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>396000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>402000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>345000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>308000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>256000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>248000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>259000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>226000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>196000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>188000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>176000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>212000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>302000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>293000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,46 +988,47 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>31000</v>
+        <v>33000</v>
       </c>
       <c r="E12" s="3">
         <v>31000</v>
       </c>
       <c r="F12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="G12" s="3">
         <v>29000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>21000</v>
       </c>
       <c r="P12" s="3">
         <v>21000</v>
@@ -1023,25 +1037,28 @@
         <v>21000</v>
       </c>
       <c r="R12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="S12" s="3">
         <v>20000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>33000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>36000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1105,8 +1122,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1116,88 +1136,91 @@
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3">
         <v>5000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="3">
         <v>9000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-14000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>39000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>117000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>51000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>137000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>31000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>441000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>852000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>41000</v>
+        <v>89000</v>
       </c>
       <c r="E15" s="3">
-        <v>41000</v>
+        <v>86000</v>
       </c>
       <c r="F15" s="3">
-        <v>39000</v>
+        <v>85000</v>
       </c>
       <c r="G15" s="3">
-        <v>37000</v>
+        <v>83000</v>
       </c>
       <c r="H15" s="3">
-        <v>40000</v>
+        <v>83000</v>
       </c>
       <c r="I15" s="3">
-        <v>40000</v>
+        <v>81000</v>
       </c>
       <c r="J15" s="3">
+        <v>80000</v>
+      </c>
+      <c r="K15" s="3">
         <v>38000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>39000</v>
       </c>
       <c r="L15" s="3">
         <v>39000</v>
@@ -1217,8 +1240,8 @@
       <c r="Q15" s="3">
         <v>39000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>11</v>
+      <c r="R15" s="3">
+        <v>39000</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>11</v>
@@ -1235,8 +1258,11 @@
       <c r="W15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1283,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1166000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1141000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1125000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1151000</v>
-      </c>
       <c r="G17" s="3">
+        <v>1146000</v>
+      </c>
+      <c r="H17" s="3">
         <v>1095000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1073000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1001000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1043000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1001000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>960000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>920000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1043000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>933000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>878000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>845000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>949000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>867000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1318000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2046000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E18" s="3">
         <v>264000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>233000</v>
       </c>
-      <c r="F18" s="3">
-        <v>211000</v>
-      </c>
       <c r="G18" s="3">
+        <v>216000</v>
+      </c>
+      <c r="H18" s="3">
         <v>218000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>201000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>185000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>166000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>119000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>104000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-78000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-107000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-60000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-497000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-831000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5373000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,161 +1445,168 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-54000</v>
+        <v>41000</v>
       </c>
       <c r="E20" s="3">
-        <v>-51000</v>
+        <v>30000</v>
       </c>
       <c r="F20" s="3">
-        <v>-62000</v>
+        <v>22000</v>
       </c>
       <c r="G20" s="3">
-        <v>-54000</v>
+        <v>31000</v>
       </c>
       <c r="H20" s="3">
-        <v>-127000</v>
+        <v>24000</v>
       </c>
       <c r="I20" s="3">
-        <v>-66000</v>
+        <v>96000</v>
       </c>
       <c r="J20" s="3">
+        <v>35000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-69000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-56000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-80000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-64000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-59000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-73000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-74000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-67000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-99000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-70000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-83000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-41000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>320000</v>
+      </c>
+      <c r="F21" s="3">
         <v>296000</v>
       </c>
-      <c r="E21" s="3">
-        <v>267000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>232000</v>
-      </c>
       <c r="G21" s="3">
-        <v>247000</v>
+        <v>268000</v>
       </c>
       <c r="H21" s="3">
-        <v>155000</v>
+        <v>277000</v>
       </c>
       <c r="I21" s="3">
-        <v>199000</v>
+        <v>186000</v>
       </c>
       <c r="J21" s="3">
+        <v>230000</v>
+      </c>
+      <c r="K21" s="3">
         <v>181000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>151000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>114000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>41000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>51000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>56000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-58000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-42000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-454000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-757000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5456000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1607,138 +1647,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E23" s="3">
         <v>210000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>182000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>149000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>164000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>74000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>119000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>97000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>63000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-137000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-61000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-87000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-174000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-159000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-567000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-914000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5332000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E24" s="3">
         <v>73000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>59000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>38000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>44000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>68000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1851,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E26" s="3">
         <v>137000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>123000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>147000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>131000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>90000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>81000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>76000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-74000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-157000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-89000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-110000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-195000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-167000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-579000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-958000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5264000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E27" s="3">
         <v>125000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>140000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>123000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>82000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>72000</v>
       </c>
       <c r="J27" s="3">
         <v>72000</v>
       </c>
       <c r="K27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="L27" s="3">
         <v>28000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-80000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-161000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-95000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-116000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-174000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-581000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-966000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5253000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2055,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2123,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2259,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>54000</v>
+        <v>-41000</v>
       </c>
       <c r="E32" s="3">
-        <v>51000</v>
+        <v>-30000</v>
       </c>
       <c r="F32" s="3">
-        <v>62000</v>
+        <v>-22000</v>
       </c>
       <c r="G32" s="3">
-        <v>54000</v>
+        <v>-31000</v>
       </c>
       <c r="H32" s="3">
-        <v>127000</v>
+        <v>-24000</v>
       </c>
       <c r="I32" s="3">
-        <v>66000</v>
+        <v>-96000</v>
       </c>
       <c r="J32" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="K32" s="3">
         <v>69000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>56000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>80000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>64000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>59000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>73000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>83000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>74000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>67000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>99000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>70000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>83000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>41000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E33" s="3">
         <v>125000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>140000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>123000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>82000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>72000</v>
       </c>
       <c r="J33" s="3">
         <v>72000</v>
       </c>
       <c r="K33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="L33" s="3">
         <v>28000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-80000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-161000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-95000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-116000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-174000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-581000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-966000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5253000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2463,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E35" s="3">
         <v>125000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>140000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>123000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>82000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>72000</v>
       </c>
       <c r="J35" s="3">
         <v>72000</v>
       </c>
       <c r="K35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="L35" s="3">
         <v>28000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-80000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-161000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-95000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-116000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-174000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-581000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-966000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5253000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2658,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>920000</v>
+      </c>
+      <c r="E41" s="3">
         <v>862000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>824000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>958000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>839000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>787000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>833000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>910000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>933000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>879000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>841000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>951000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1291000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1217000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1177000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1118000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1121000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>680000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>670000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>618000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,288 +2792,303 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1372000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1303000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1277000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1318000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1120000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1123000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1028000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>927000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>930000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>868000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>825000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>816000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>782000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>793000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>833000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>836000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>929000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1206000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1244000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>919000</v>
+      </c>
+      <c r="E44" s="3">
         <v>884000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>850000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>788000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>776000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>751000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>719000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>689000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>723000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>716000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>684000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>670000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>681000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>662000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>676000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>717000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>811000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>862000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1004000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>972000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>244000</v>
+        <v>204000</v>
       </c>
       <c r="E45" s="3">
-        <v>335000</v>
+        <v>186000</v>
       </c>
       <c r="F45" s="3">
-        <v>322000</v>
+        <v>222000</v>
       </c>
       <c r="G45" s="3">
-        <v>287000</v>
+        <v>217000</v>
       </c>
       <c r="H45" s="3">
-        <v>313000</v>
+        <v>180000</v>
       </c>
       <c r="I45" s="3">
-        <v>368000</v>
+        <v>178000</v>
       </c>
       <c r="J45" s="3">
+        <v>218000</v>
+      </c>
+      <c r="K45" s="3">
         <v>416000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>480000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>485000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>496000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>465000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>456000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>465000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>512000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>509000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>525000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>456000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>494000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>619000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3400000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3362000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3312000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3345000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3220000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>3043000</v>
       </c>
       <c r="J46" s="3">
         <v>3043000</v>
       </c>
       <c r="K46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="L46" s="3">
         <v>3063000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3010000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2889000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2911000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3244000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3126000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3158000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3177000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3293000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2927000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3374000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3453000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>28000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>26000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>28000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>27000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>25000</v>
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>11</v>
@@ -3003,8 +3108,8 @@
       <c r="O47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3027,138 +3132,147 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1183000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1145000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1123000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1095000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1054000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1033000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1049000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1033000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1019000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1054000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1083000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1109000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1139000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1234000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1298000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1374000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1451000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1522000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1726000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2378000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>356000</v>
+      </c>
+      <c r="E49" s="3">
         <v>384000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>417000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>370000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>404000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>440000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>474000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>506000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>540000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>579000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>619000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>657000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>695000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>734000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>771000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>810000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>841000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>875000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1000000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1353000</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,73 +3404,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E52" s="3">
         <v>192000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>212000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>234000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>189000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>177000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>118000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>138000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>85000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>92000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>93000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>97000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>70000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>68000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>73000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>79000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>85000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>65000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>109000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3540,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5188000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5111000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5090000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5068000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4895000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4648000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4709000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4720000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4707000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4735000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4684000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4774000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5148000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5160000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5295000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5434000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5664000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5409000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6165000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7293000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,398 +3662,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>723000</v>
+      </c>
+      <c r="E57" s="3">
         <v>771000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>716000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>679000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>620000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>502000</v>
       </c>
       <c r="I57" s="3">
         <v>502000</v>
       </c>
       <c r="J57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="K57" s="3">
         <v>460000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>425000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>448000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>385000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>380000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>350000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>348000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>330000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>325000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>332000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>384000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>544000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>585000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20000</v>
+        <v>67000</v>
       </c>
       <c r="E58" s="3">
-        <v>101000</v>
+        <v>66000</v>
       </c>
       <c r="F58" s="3">
-        <v>168000</v>
+        <v>148000</v>
       </c>
       <c r="G58" s="3">
-        <v>91000</v>
+        <v>214000</v>
       </c>
       <c r="H58" s="3">
-        <v>33000</v>
+        <v>134000</v>
       </c>
       <c r="I58" s="3">
-        <v>120000</v>
+        <v>75000</v>
       </c>
       <c r="J58" s="3">
+        <v>164000</v>
+      </c>
+      <c r="K58" s="3">
         <v>45000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>64000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>211000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>13000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>900000</v>
+        <v>549000</v>
       </c>
       <c r="E59" s="3">
-        <v>983000</v>
+        <v>561000</v>
       </c>
       <c r="F59" s="3">
-        <v>1019000</v>
+        <v>638000</v>
       </c>
       <c r="G59" s="3">
-        <v>1020000</v>
+        <v>586000</v>
       </c>
       <c r="H59" s="3">
-        <v>929000</v>
+        <v>592000</v>
       </c>
       <c r="I59" s="3">
-        <v>889000</v>
+        <v>575000</v>
       </c>
       <c r="J59" s="3">
+        <v>523000</v>
+      </c>
+      <c r="K59" s="3">
         <v>965000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>945000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>871000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>902000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>940000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>963000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>885000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1023000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1024000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1070000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1074000</v>
       </c>
       <c r="V59" s="3">
         <v>1074000</v>
       </c>
       <c r="W59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="X59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1667000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1691000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1800000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1866000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1731000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1464000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1511000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1470000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1384000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1383000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1300000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1332000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1524000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1243000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1364000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1362000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1416000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1426000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1644000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1672000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1628000</v>
+        <v>1749000</v>
       </c>
       <c r="E61" s="3">
-        <v>1629000</v>
+        <v>1755000</v>
       </c>
       <c r="F61" s="3">
-        <v>1715000</v>
+        <v>1753000</v>
       </c>
       <c r="G61" s="3">
-        <v>1864000</v>
+        <v>1846000</v>
       </c>
       <c r="H61" s="3">
         <v>1993000</v>
       </c>
       <c r="I61" s="3">
-        <v>2067000</v>
+        <v>2118000</v>
       </c>
       <c r="J61" s="3">
+        <v>2197000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2366000</v>
       </c>
       <c r="L61" s="3">
         <v>2366000</v>
       </c>
       <c r="M61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="N61" s="3">
         <v>2416000</v>
       </c>
       <c r="O61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="P61" s="3">
         <v>2431000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2605000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2602000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2601000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2602000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2148000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2149000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2151000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>552000</v>
+        <v>413000</v>
       </c>
       <c r="E62" s="3">
-        <v>561000</v>
+        <v>422000</v>
       </c>
       <c r="F62" s="3">
-        <v>565000</v>
+        <v>433000</v>
       </c>
       <c r="G62" s="3">
-        <v>537000</v>
+        <v>299000</v>
       </c>
       <c r="H62" s="3">
-        <v>519000</v>
+        <v>405000</v>
       </c>
       <c r="I62" s="3">
-        <v>545000</v>
+        <v>391000</v>
       </c>
       <c r="J62" s="3">
+        <v>413000</v>
+      </c>
+      <c r="K62" s="3">
         <v>496000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>485000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>495000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>542000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>530000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>546000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>553000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>508000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>534000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>523000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>530000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>509000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>554000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4272,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3883000</v>
+        <v>3832000</v>
       </c>
       <c r="E66" s="3">
-        <v>3999000</v>
+        <v>3871000</v>
       </c>
       <c r="F66" s="3">
-        <v>4144000</v>
+        <v>3990000</v>
       </c>
       <c r="G66" s="3">
-        <v>4153000</v>
+        <v>4146000</v>
       </c>
       <c r="H66" s="3">
-        <v>4003000</v>
+        <v>4132000</v>
       </c>
       <c r="I66" s="3">
+        <v>3976000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>4123000</v>
+      </c>
+      <c r="K66" s="3">
+        <v>4185000</v>
+      </c>
+      <c r="L66" s="3">
+        <v>4254000</v>
+      </c>
+      <c r="M66" s="3">
+        <v>4269000</v>
+      </c>
+      <c r="N66" s="3">
+        <v>4288000</v>
+      </c>
+      <c r="O66" s="3">
+        <v>4302000</v>
+      </c>
+      <c r="P66" s="3">
+        <v>4527000</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>4434000</v>
+      </c>
+      <c r="R66" s="3">
+        <v>4508000</v>
+      </c>
+      <c r="S66" s="3">
+        <v>4527000</v>
+      </c>
+      <c r="T66" s="3">
+        <v>4577000</v>
+      </c>
+      <c r="U66" s="3">
         <v>4142000</v>
       </c>
-      <c r="J66" s="3">
-        <v>4185000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>4254000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>4269000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>4288000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>4302000</v>
-      </c>
-      <c r="O66" s="3">
-        <v>4527000</v>
-      </c>
-      <c r="P66" s="3">
-        <v>4434000</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>4508000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>4527000</v>
-      </c>
-      <c r="S66" s="3">
-        <v>4577000</v>
-      </c>
-      <c r="T66" s="3">
-        <v>4142000</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4346000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4413000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4638,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1579000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-992000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-26000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4910,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1345000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1228000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1091000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>924000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>742000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>645000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>567000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>535000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>453000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>466000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>396000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>472000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>621000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>726000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>787000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>907000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1087000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1267000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1819000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2880000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5046,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E81" s="3">
         <v>125000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>140000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>123000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>82000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>72000</v>
       </c>
       <c r="J81" s="3">
         <v>72000</v>
       </c>
       <c r="K81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="L81" s="3">
         <v>28000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-80000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-161000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-95000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-116000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-174000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-581000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-966000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5253000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,73 +5215,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>86000</v>
+        <v>46000</v>
       </c>
       <c r="E83" s="3">
-        <v>85000</v>
+        <v>41000</v>
       </c>
       <c r="F83" s="3">
-        <v>83000</v>
+        <v>40000</v>
       </c>
       <c r="G83" s="3">
-        <v>83000</v>
+        <v>46000</v>
       </c>
       <c r="H83" s="3">
-        <v>81000</v>
+        <v>49000</v>
       </c>
       <c r="I83" s="3">
-        <v>80000</v>
+        <v>51000</v>
       </c>
       <c r="J83" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K83" s="3">
         <v>84000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>88000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>90000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>87000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>103000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>112000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>114000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>111000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>116000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>117000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>113000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>157000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>124000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5621,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E89" s="3">
         <v>150000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>131000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>375000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>172000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>201000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>84000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>193000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>160000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>60000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-64000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>114000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>46000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>74000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>127000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5717,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-59000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-67000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-64000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-49000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-35000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-38000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-93000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5919,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-54000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-131000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-32000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-81000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>21000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-75000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,31 +6015,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>18000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5847,8 +6081,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,199 +6285,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-102000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-187000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-126000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-91000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-170000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-127000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-159000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-64000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-338000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-50000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-52000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>412000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-170000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-34000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-22000</v>
-      </c>
       <c r="J101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-33000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>8000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-11000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-126000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>117000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>24000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-61000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-129000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>34000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-57000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-333000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>59000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>44000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>58000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>537000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-36000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-250000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>WFRD</t>
   </si>
@@ -656,315 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1341000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1409000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1405000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1358000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1362000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1313000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1274000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1186000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1209000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1120000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1064000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>938000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>965000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>945000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>903000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>832000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>842000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>807000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>821000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1215000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1246000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>913000</v>
+      </c>
+      <c r="E9" s="3">
         <v>917000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>891000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>884000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>899000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>859000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>847000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>790000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>807000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>775000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>756000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>682000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>717000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>686000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>677000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>636000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>654000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>631000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>609000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>913000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>953000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E10" s="3">
         <v>492000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>514000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>474000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>463000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>454000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>427000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>396000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>402000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>345000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>308000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>256000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>248000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>259000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>226000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>196000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>188000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>176000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>212000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>302000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>293000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -989,49 +1001,50 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E12" s="3">
         <v>33000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>31000</v>
       </c>
       <c r="F12" s="3">
         <v>31000</v>
       </c>
       <c r="G12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="H12" s="3">
         <v>29000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>21000</v>
       </c>
       <c r="Q12" s="3">
         <v>21000</v>
@@ -1040,25 +1053,28 @@
         <v>21000</v>
       </c>
       <c r="S12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="T12" s="3">
         <v>20000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>33000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>36000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1125,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1139,8 +1158,8 @@
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3">
-        <v>5000</v>
+      <c r="G14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>11</v>
@@ -1151,79 +1170,82 @@
       <c r="J14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="3">
         <v>9000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-14000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>39000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>117000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>51000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-8000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>137000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>31000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>441000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>852000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E15" s="3">
         <v>89000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>86000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>85000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>83000</v>
       </c>
       <c r="H15" s="3">
         <v>83000</v>
       </c>
       <c r="I15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="J15" s="3">
         <v>81000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>80000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>38000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>39000</v>
       </c>
       <c r="M15" s="3">
         <v>39000</v>
@@ -1243,8 +1265,8 @@
       <c r="R15" s="3">
         <v>39000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>11</v>
+      <c r="S15" s="3">
+        <v>39000</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>11</v>
@@ -1261,8 +1283,11 @@
       <c r="X15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1143000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1166000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1141000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1125000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1146000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1095000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1073000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1001000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1043000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1001000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>960000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>920000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1043000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>933000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>878000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>845000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>949000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>867000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1318000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2046000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E18" s="3">
         <v>243000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>264000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>233000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>216000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>218000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>201000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>185000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>166000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>119000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>104000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-78000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-107000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-60000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-497000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-831000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5373000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,144 +1478,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>41000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>30000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>22000</v>
       </c>
-      <c r="G20" s="3">
-        <v>31000</v>
-      </c>
       <c r="H20" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I20" s="3">
         <v>24000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>96000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>35000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-69000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-56000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-80000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-64000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-59000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-83000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-74000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-67000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-99000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-70000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-83000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-41000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E21" s="3">
         <v>291000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>320000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>296000</v>
       </c>
-      <c r="G21" s="3">
-        <v>268000</v>
-      </c>
       <c r="H21" s="3">
+        <v>263000</v>
+      </c>
+      <c r="I21" s="3">
         <v>277000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>186000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>230000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>181000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>151000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>114000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>51000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>56000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-58000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-42000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-454000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-757000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5456000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1591,25 +1630,25 @@
         <v>37000</v>
       </c>
       <c r="E22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F22" s="3">
         <v>41000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>43000</v>
       </c>
       <c r="G22" s="3">
         <v>43000</v>
       </c>
       <c r="H22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I22" s="3">
         <v>45000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>47000</v>
       </c>
       <c r="J22" s="3">
         <v>47000</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1650,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E23" s="3">
         <v>178000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>210000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>182000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>149000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>164000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>74000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>119000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>97000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>63000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-137000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-61000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-58000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-87000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-174000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-159000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-567000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-914000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5332000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E24" s="3">
         <v>12000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>73000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>59000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>38000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>44000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>68000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E26" s="3">
         <v>166000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>137000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>123000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>147000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>131000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>90000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>76000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-74000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-157000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-73000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-110000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-195000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-167000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-579000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-958000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5264000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>157000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>125000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>140000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>123000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>82000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>72000</v>
       </c>
       <c r="K27" s="3">
         <v>72000</v>
       </c>
       <c r="L27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="M27" s="3">
         <v>28000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-80000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-161000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-78000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-116000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-174000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-581000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-966000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5253000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-41000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-30000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-22000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-31000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-24000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-96000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-35000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>69000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>56000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>80000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>64000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>59000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>73000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>83000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>74000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>67000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>99000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>70000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>83000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>41000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>157000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>125000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>112000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>140000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>123000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>82000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>72000</v>
       </c>
       <c r="K33" s="3">
         <v>72000</v>
       </c>
       <c r="L33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="M33" s="3">
         <v>28000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-80000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-161000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-78000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-116000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-174000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-581000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-966000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5253000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>157000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>125000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>112000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>140000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>123000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>82000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>72000</v>
       </c>
       <c r="K35" s="3">
         <v>72000</v>
       </c>
       <c r="L35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="M35" s="3">
         <v>28000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-80000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-161000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-78000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-116000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-174000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-581000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-966000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5253000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,76 +2744,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E41" s="3">
         <v>920000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>862000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>824000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>958000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>839000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>787000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>833000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>910000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>933000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>879000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>841000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>951000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1291000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1217000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1177000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1118000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1121000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>680000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>670000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>618000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,280 +2884,295 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1322000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1299000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1372000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1303000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1277000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1318000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1120000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1123000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1028000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>927000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>930000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>868000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>825000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>816000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>782000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>793000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>833000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>836000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>929000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1206000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1244000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E44" s="3">
         <v>919000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>884000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>850000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>788000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>776000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>751000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>719000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>689000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>723000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>716000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>684000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>670000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>681000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>662000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>676000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>717000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>811000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>862000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1004000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>972000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E45" s="3">
         <v>204000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>186000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>222000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>217000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>180000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>178000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>218000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>416000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>480000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>485000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>496000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>465000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>456000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>465000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>512000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>509000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>525000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>456000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>494000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>619000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3402000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3400000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3362000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3312000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3345000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3220000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>3043000</v>
       </c>
       <c r="K46" s="3">
         <v>3043000</v>
       </c>
       <c r="L46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="M46" s="3">
         <v>3063000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3010000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2889000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2911000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3244000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3126000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3158000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3177000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3293000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2927000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3374000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3453000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3111,8 +3215,8 @@
       <c r="P47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3135,144 +3239,153 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1183000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1145000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1123000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1095000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1054000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1033000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1049000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1033000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1019000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1054000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1083000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1109000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1139000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1234000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1298000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1374000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1451000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1522000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1726000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2378000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E49" s="3">
         <v>356000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>384000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>417000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>370000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>404000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>440000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>474000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>506000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>540000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>579000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>619000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>657000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>695000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>734000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>771000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>810000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>841000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>875000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1000000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1353000</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E52" s="3">
         <v>217000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>192000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>212000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>234000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>189000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>177000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>118000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>138000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>85000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>92000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>93000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>97000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>68000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>73000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>79000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>85000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>65000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>109000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5159000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5188000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5111000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5090000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5068000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4895000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4648000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4709000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4720000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4707000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4735000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4684000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4774000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5148000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5160000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5295000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5434000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5664000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5409000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6165000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7293000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,416 +3792,435 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>792000</v>
+      </c>
+      <c r="E57" s="3">
         <v>723000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>771000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>716000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>679000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>620000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>502000</v>
       </c>
       <c r="J57" s="3">
         <v>502000</v>
       </c>
       <c r="K57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="L57" s="3">
         <v>460000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>425000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>448000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>385000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>380000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>350000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>348000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>330000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>325000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>332000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>384000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>544000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>585000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E58" s="3">
         <v>67000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>66000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>148000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>214000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>134000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>75000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>164000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>64000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>211000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>14000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>541000</v>
+      </c>
+      <c r="E59" s="3">
         <v>549000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>561000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>638000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>586000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>592000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>575000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>523000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>965000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>945000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>871000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>902000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>940000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>963000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>885000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1023000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1024000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1070000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1074000</v>
       </c>
       <c r="W59" s="3">
         <v>1074000</v>
       </c>
       <c r="X59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1696000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1667000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1691000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1800000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1866000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1731000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1464000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1511000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1470000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1384000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1383000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1300000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1332000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1524000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1243000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1364000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1362000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1416000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1426000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1644000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1672000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1727000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1749000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1755000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1753000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1846000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1993000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2118000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2197000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2366000</v>
       </c>
       <c r="M61" s="3">
         <v>2366000</v>
       </c>
       <c r="N61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="O61" s="3">
         <v>2416000</v>
       </c>
       <c r="P61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2431000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2605000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2602000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2601000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2602000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2148000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2149000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2151000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E62" s="3">
         <v>413000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>422000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>433000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>299000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>405000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>391000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>413000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>496000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>485000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>495000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>542000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>530000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>546000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>553000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>508000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>534000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>523000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>530000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>509000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>554000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3876000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3832000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3871000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3990000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4146000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4132000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3976000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4123000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4185000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4254000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4269000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4288000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4302000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4527000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4434000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4508000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4527000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4577000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4142000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4346000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4413000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1486000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1579000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-992000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-26000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1285000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1345000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1228000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1091000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>924000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>742000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>645000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>567000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>535000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>453000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>466000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>396000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>472000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>621000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>726000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>787000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>907000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1087000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1267000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1819000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2880000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>157000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>125000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>112000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>140000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>123000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>82000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>72000</v>
       </c>
       <c r="K81" s="3">
         <v>72000</v>
       </c>
       <c r="L81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="M81" s="3">
         <v>28000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-80000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-161000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-78000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-116000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-174000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-581000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-966000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5253000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E83" s="3">
         <v>46000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>41000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>40000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>51000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>48000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>84000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>88000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>90000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>87000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>103000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>112000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>114000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>111000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>116000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>117000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>113000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>157000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>124000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E89" s="3">
         <v>262000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>150000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>131000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>375000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>172000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>201000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>84000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>193000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>160000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-64000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>88000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>114000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>46000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>74000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>127000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>31000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>30000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-62000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-59000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-67000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-64000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-49000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-54000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-35000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-38000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-93000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-92000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-61000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-54000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-131000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-32000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-81000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>21000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-51000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-75000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,16 +6248,17 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
         <v>18000</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>11</v>
+      <c r="E96" s="3">
+        <v>18000</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>11</v>
@@ -6042,8 +6275,8 @@
       <c r="J96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6084,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-89000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-187000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-126000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-91000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-170000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-127000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-159000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-64000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-338000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-52000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>412000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-170000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-34000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-33000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-11000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>58000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-126000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>117000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-61000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-129000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-57000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-333000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>59000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>44000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>58000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>537000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-36000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-250000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1193000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1341000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1409000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1405000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1358000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1362000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1313000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1274000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1186000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1209000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1120000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1064000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>938000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>965000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>945000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>903000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>832000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>842000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>807000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>821000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1215000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1246000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E9" s="3">
         <v>913000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>917000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>891000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>884000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>899000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>859000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>847000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>790000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>807000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>775000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>756000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>682000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>717000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>686000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>677000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>636000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>654000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>631000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>609000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>913000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>953000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E10" s="3">
         <v>428000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>492000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>514000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>474000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>463000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>454000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>427000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>396000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>402000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>345000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>308000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>256000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>248000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>259000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>226000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>196000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>188000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>176000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>212000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>302000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>293000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,52 +1015,53 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E12" s="3">
         <v>28000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>31000</v>
       </c>
       <c r="G12" s="3">
         <v>31000</v>
       </c>
       <c r="H12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>21000</v>
       </c>
       <c r="R12" s="3">
         <v>21000</v>
@@ -1056,25 +1070,28 @@
         <v>21000</v>
       </c>
       <c r="T12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="U12" s="3">
         <v>20000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>23000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>33000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>36000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,13 +1161,16 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>11</v>
+      <c r="D14" s="3">
+        <v>29000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -1161,8 +1181,8 @@
       <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>11</v>
+      <c r="H14" s="3">
+        <v>3000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>11</v>
@@ -1173,82 +1193,85 @@
       <c r="K14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="3">
         <v>9000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-14000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>39000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>117000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>51000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-8000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>137000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>31000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>441000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>852000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E15" s="3">
         <v>83000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>89000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>86000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>85000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>83000</v>
       </c>
       <c r="I15" s="3">
         <v>83000</v>
       </c>
       <c r="J15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K15" s="3">
         <v>81000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>80000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>38000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>39000</v>
       </c>
       <c r="N15" s="3">
         <v>39000</v>
@@ -1268,8 +1291,8 @@
       <c r="S15" s="3">
         <v>39000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>11</v>
+      <c r="T15" s="3">
+        <v>39000</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>11</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1022000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1143000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1166000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1141000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1125000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1122000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1146000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1095000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1073000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1001000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1043000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1001000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>960000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>920000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1043000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>933000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>878000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>845000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>949000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>867000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1318000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2046000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E18" s="3">
         <v>198000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>243000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>264000</v>
       </c>
-      <c r="G18" s="3">
-        <v>233000</v>
-      </c>
       <c r="H18" s="3">
+        <v>236000</v>
+      </c>
+      <c r="I18" s="3">
         <v>216000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>218000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>201000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>185000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>166000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>119000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>104000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>25000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-107000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-60000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-497000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-831000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5373000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,150 +1512,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>22000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>36000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>24000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>96000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>35000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-69000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-56000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-80000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-64000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-73000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-83000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-74000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-67000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-99000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-70000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-83000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E21" s="3">
         <v>277000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>291000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>320000</v>
       </c>
-      <c r="G21" s="3">
-        <v>296000</v>
-      </c>
       <c r="H21" s="3">
+        <v>299000</v>
+      </c>
+      <c r="I21" s="3">
         <v>263000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>277000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>186000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>230000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>181000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>151000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>114000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>41000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>51000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>56000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-58000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-42000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-454000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-757000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5456000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1633,25 +1673,25 @@
         <v>37000</v>
       </c>
       <c r="F22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="G22" s="3">
         <v>41000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>43000</v>
       </c>
       <c r="H22" s="3">
         <v>43000</v>
       </c>
       <c r="I22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="J22" s="3">
         <v>45000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>47000</v>
       </c>
       <c r="K22" s="3">
         <v>47000</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1692,150 +1732,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E23" s="3">
         <v>169000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>178000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>210000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>182000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>149000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>164000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>74000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>119000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>97000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>63000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-137000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-61000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-58000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-87000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-174000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-159000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-567000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-914000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5332000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E24" s="3">
         <v>45000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>73000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>21000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>44000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>68000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E26" s="3">
         <v>124000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>166000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>137000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>123000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>147000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>131000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>90000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>76000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-74000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-89000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-73000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-110000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-195000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-167000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-579000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-958000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5264000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E27" s="3">
         <v>112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>157000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>125000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>112000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>140000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>123000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>82000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>72000</v>
       </c>
       <c r="L27" s="3">
         <v>72000</v>
       </c>
       <c r="M27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="N27" s="3">
         <v>28000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-80000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-95000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-78000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-116000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-174000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-581000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-966000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5253000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-22000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-36000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-24000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-96000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-35000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>69000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>56000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>80000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>64000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>59000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>73000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>83000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>74000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>67000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>99000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>70000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>83000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>41000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E33" s="3">
         <v>112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>157000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>125000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>112000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>140000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>123000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>82000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>72000</v>
       </c>
       <c r="L33" s="3">
         <v>72000</v>
       </c>
       <c r="M33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="N33" s="3">
         <v>28000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-80000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-95000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-78000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-116000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-174000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-581000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-966000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5253000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E35" s="3">
         <v>112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>157000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>125000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>112000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>140000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>123000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>82000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>72000</v>
       </c>
       <c r="L35" s="3">
         <v>72000</v>
       </c>
       <c r="M35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="N35" s="3">
         <v>28000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-80000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-95000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-78000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-116000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-174000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-581000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-966000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5253000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2831,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>873000</v>
+      </c>
+      <c r="E41" s="3">
         <v>916000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>920000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>862000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>824000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>958000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>839000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>787000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>833000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>910000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>933000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>879000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>841000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>951000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1291000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1217000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1177000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1118000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1121000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>680000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>670000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>618000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,292 +2977,307 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1218000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1322000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1299000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1372000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1303000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1277000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1318000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1120000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1123000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1028000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>927000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>930000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>868000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>825000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>816000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>782000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>793000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>833000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>836000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>929000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1206000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1244000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>889000</v>
+      </c>
+      <c r="E44" s="3">
         <v>880000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>919000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>884000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>850000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>788000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>776000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>751000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>719000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>689000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>723000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>716000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>684000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>670000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>681000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>662000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>676000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>717000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>811000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>862000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1004000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>972000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E45" s="3">
         <v>225000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>204000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>186000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>222000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>217000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>180000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>178000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>218000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>416000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>480000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>485000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>496000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>465000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>456000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>465000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>512000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>509000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>525000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>456000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>494000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>619000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3402000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3400000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3362000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3312000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3345000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3220000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="K46" s="3">
-        <v>3043000</v>
       </c>
       <c r="L46" s="3">
         <v>3043000</v>
       </c>
       <c r="M46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="N46" s="3">
         <v>3063000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3010000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2889000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2911000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3244000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3126000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3158000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3177000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3293000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2927000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3374000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3453000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3218,8 +3323,8 @@
       <c r="Q47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3242,150 +3347,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1185000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1183000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1145000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1123000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1095000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1054000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1033000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1049000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1033000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1019000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1054000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1083000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1109000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1139000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1234000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1298000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1374000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1451000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1522000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1726000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2378000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E49" s="3">
         <v>325000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>356000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>384000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>417000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>370000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>404000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>440000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>474000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>506000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>540000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>579000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>619000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>657000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>695000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>734000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>771000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>810000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>841000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>875000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1000000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1353000</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3643,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3535,70 +3655,73 @@
         <v>213000</v>
       </c>
       <c r="E52" s="3">
+        <v>213000</v>
+      </c>
+      <c r="F52" s="3">
         <v>217000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>192000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>212000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>234000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>189000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>177000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>118000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>138000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>85000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>92000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>93000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>97000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>70000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>66000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>68000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>73000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>79000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>85000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>65000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>109000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5054000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5159000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5188000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5111000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5090000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5068000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4895000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4648000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4709000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4720000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4707000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4735000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4684000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4774000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5148000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5160000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5295000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5434000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5664000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5409000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6165000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7293000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,434 +3923,453 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>714000</v>
+      </c>
+      <c r="E57" s="3">
         <v>792000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>723000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>771000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>716000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>679000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>620000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>502000</v>
       </c>
       <c r="K57" s="3">
         <v>502000</v>
       </c>
       <c r="L57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="M57" s="3">
         <v>460000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>425000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>448000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>385000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>380000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>350000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>348000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>330000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>325000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>332000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>384000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>544000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>585000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E58" s="3">
         <v>61000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>148000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>214000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>134000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>75000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>164000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>45000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>64000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>211000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>14000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>26000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E59" s="3">
         <v>541000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>549000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>561000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>638000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>586000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>592000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>575000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>523000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>965000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>945000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>871000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>902000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>940000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>963000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>885000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1023000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1024000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1070000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1074000</v>
       </c>
       <c r="X59" s="3">
         <v>1074000</v>
       </c>
       <c r="Y59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1696000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1667000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1691000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1800000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1866000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1731000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1464000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1511000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1470000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1384000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1383000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1300000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1332000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1524000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1243000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1364000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1362000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1416000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1426000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1644000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1672000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1691000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1727000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1749000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1755000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1753000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1846000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1993000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2118000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2197000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2366000</v>
       </c>
       <c r="N61" s="3">
         <v>2366000</v>
       </c>
       <c r="O61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="P61" s="3">
         <v>2416000</v>
       </c>
       <c r="Q61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="R61" s="3">
         <v>2431000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2605000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2602000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2601000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2602000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2148000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2149000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2151000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E62" s="3">
         <v>325000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>413000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>422000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>433000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>299000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>405000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>391000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>413000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>496000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>485000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>495000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>542000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>530000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>546000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>553000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>508000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>534000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>523000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>530000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>509000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>554000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3694000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3876000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3832000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3871000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3990000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4146000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4132000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3976000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4123000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4185000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4254000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4269000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4288000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4302000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4527000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4434000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4508000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4527000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4577000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4142000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4346000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4413000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1428000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1486000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1579000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-992000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1352000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1285000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1345000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1228000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1091000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>924000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>742000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>645000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>567000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>535000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>453000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>466000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>396000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>472000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>621000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>726000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>787000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>907000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1087000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1267000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1819000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2880000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E81" s="3">
         <v>112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>157000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>125000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>112000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>140000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>123000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>82000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>72000</v>
       </c>
       <c r="L81" s="3">
         <v>72000</v>
       </c>
       <c r="M81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="N81" s="3">
         <v>28000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-80000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-95000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-78000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-116000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-174000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-581000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-966000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5253000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5423,70 +5622,73 @@
         <v>44000</v>
       </c>
       <c r="E83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F83" s="3">
         <v>46000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>41000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>40000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>49000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>51000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>48000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>84000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>88000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>90000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>87000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>103000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>112000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>114000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>111000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>116000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>117000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>113000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>157000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>124000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E89" s="3">
         <v>249000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>262000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>150000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>131000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>375000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>172000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>201000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>84000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>193000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>160000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>60000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-64000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>114000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>46000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>74000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>127000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>31000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>30000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6158,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-78000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-64000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-54000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-35000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-38000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-93000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-131000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-58000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-32000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-29000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>21000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-51000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-75000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6260,8 +6494,8 @@
       <c r="E96" s="3">
         <v>18000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>11</v>
+      <c r="F96" s="3">
+        <v>18000</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>11</v>
@@ -6278,8 +6512,8 @@
       <c r="K96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,8 +6776,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6542,208 +6788,217 @@
         <v>-133000</v>
       </c>
       <c r="E100" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-89000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-187000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-126000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-91000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-170000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-127000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-159000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-64000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-20000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-338000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-50000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-52000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>412000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-170000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-34000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-33000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-11000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>58000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-126000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>117000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>24000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-61000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-129000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-31000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>34000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-57000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-333000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>59000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>44000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>58000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>537000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-36000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-250000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -656,340 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1204000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1193000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1341000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1409000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1405000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1358000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1362000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1313000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1274000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1186000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1209000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1120000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1064000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>938000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>965000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>945000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>903000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>832000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>842000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>807000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>821000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1215000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1246000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>829000</v>
+      </c>
+      <c r="E9" s="3">
         <v>819000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>913000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>917000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>891000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>884000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>899000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>859000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>847000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>790000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>807000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>775000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>756000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>682000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>717000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>686000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>677000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>636000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>654000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>631000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>609000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>913000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>953000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E10" s="3">
         <v>374000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>428000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>492000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>514000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>474000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>463000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>454000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>427000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>396000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>402000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>345000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>308000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>256000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>248000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>259000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>226000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>196000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>188000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>176000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>212000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>302000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>293000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,55 +1029,56 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="3">
         <v>29000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>31000</v>
       </c>
       <c r="H12" s="3">
         <v>31000</v>
       </c>
       <c r="I12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J12" s="3">
         <v>29000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>21000</v>
       </c>
       <c r="S12" s="3">
         <v>21000</v>
@@ -1073,25 +1087,28 @@
         <v>21000</v>
       </c>
       <c r="U12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="V12" s="3">
         <v>20000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>33000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>36000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,16 +1181,19 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E14" s="3">
         <v>29000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -1182,10 +1202,10 @@
         <v>11</v>
       </c>
       <c r="H14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="3">
         <v>3000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>11</v>
@@ -1196,85 +1216,88 @@
       <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" s="3">
         <v>9000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-14000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>117000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>51000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-8000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>137000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>31000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>441000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>852000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E15" s="3">
         <v>62000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>83000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>89000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>86000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>85000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>83000</v>
       </c>
       <c r="J15" s="3">
         <v>83000</v>
       </c>
       <c r="K15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="L15" s="3">
         <v>81000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>80000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>38000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>39000</v>
       </c>
       <c r="O15" s="3">
         <v>39000</v>
@@ -1294,8 +1317,8 @@
       <c r="T15" s="3">
         <v>39000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>11</v>
+      <c r="U15" s="3">
+        <v>39000</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>11</v>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1026000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1022000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1143000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1166000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1141000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1136000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1122000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1146000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1095000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1073000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1001000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1043000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1001000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>960000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>920000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1043000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>933000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>878000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>845000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>949000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>867000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1318000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2046000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E18" s="3">
         <v>171000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>198000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>243000</v>
       </c>
-      <c r="G18" s="3">
-        <v>264000</v>
-      </c>
       <c r="H18" s="3">
+        <v>269000</v>
+      </c>
+      <c r="I18" s="3">
         <v>236000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>216000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>218000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>201000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>185000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>166000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>119000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>104000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-78000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>25000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-107000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-60000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-497000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-831000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5373000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,161 +1546,168 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E20" s="3">
         <v>20000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>41000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>30000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>22000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>36000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>24000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>96000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>35000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-69000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-56000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-80000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-59000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-73000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-83000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-74000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-67000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-99000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-70000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-83000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E21" s="3">
         <v>213000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>277000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>291000</v>
       </c>
-      <c r="G21" s="3">
-        <v>320000</v>
-      </c>
       <c r="H21" s="3">
+        <v>325000</v>
+      </c>
+      <c r="I21" s="3">
         <v>299000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>263000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>277000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>186000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>230000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>181000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>151000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>114000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>41000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-34000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>51000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>56000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>24000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-58000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-42000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-454000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-757000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5456000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>37000</v>
+        <v>35000</v>
       </c>
       <c r="E22" s="3">
         <v>37000</v>
@@ -1676,25 +1716,25 @@
         <v>37000</v>
       </c>
       <c r="G22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="H22" s="3">
         <v>41000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>43000</v>
       </c>
       <c r="I22" s="3">
         <v>43000</v>
       </c>
       <c r="J22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="K22" s="3">
         <v>45000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>47000</v>
       </c>
       <c r="L22" s="3">
         <v>47000</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1735,156 +1775,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E23" s="3">
         <v>96000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>169000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>178000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>210000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>182000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>149000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>164000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>74000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>119000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>97000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>63000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-137000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-61000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-58000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-87000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-174000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-159000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-567000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-914000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5332000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E24" s="3">
         <v>10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>45000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>73000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>59000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>21000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>44000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>68000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E26" s="3">
         <v>86000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>124000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>166000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>137000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>123000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>147000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>131000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>90000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>76000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-157000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-89000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-73000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-110000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-195000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-167000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-579000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-958000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5264000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E27" s="3">
         <v>76000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>157000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>125000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>112000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>140000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>123000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>72000</v>
       </c>
       <c r="M27" s="3">
         <v>72000</v>
       </c>
       <c r="N27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="O27" s="3">
         <v>28000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-161000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-95000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-78000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-116000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-174000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-581000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-966000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5253000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2468,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-20000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-41000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-30000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-22000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-36000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-24000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-96000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-35000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>69000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>56000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>80000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>64000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>59000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>73000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>83000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>74000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>67000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>99000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>70000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>83000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>41000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E33" s="3">
         <v>76000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>157000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>125000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>112000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>140000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>123000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>72000</v>
       </c>
       <c r="M33" s="3">
         <v>72000</v>
       </c>
       <c r="N33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="O33" s="3">
         <v>28000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-161000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-95000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-78000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-116000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-174000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-581000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-966000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5253000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E35" s="3">
         <v>76000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>157000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>125000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>112000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>140000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>123000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>72000</v>
       </c>
       <c r="M35" s="3">
         <v>72000</v>
       </c>
       <c r="N35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="O35" s="3">
         <v>28000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-161000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-95000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-78000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-116000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-174000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-581000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-966000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5253000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2918,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>943000</v>
+      </c>
+      <c r="E41" s="3">
         <v>873000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>916000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>920000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>862000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>824000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>958000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>839000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>787000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>833000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>910000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>933000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>879000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>841000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>951000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1291000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1217000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1177000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1118000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1121000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>680000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>670000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>618000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,304 +3070,319 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1218000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1322000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1299000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1372000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1303000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1277000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1318000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1120000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1123000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1028000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>927000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>930000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>868000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>825000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>816000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>782000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>793000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>833000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>836000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>929000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1206000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1244000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>881000</v>
+      </c>
+      <c r="E44" s="3">
         <v>889000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>880000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>919000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>884000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>850000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>788000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>776000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>751000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>719000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>689000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>723000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>716000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>684000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>670000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>681000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>662000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>676000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>717000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>811000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>862000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1004000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>972000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E45" s="3">
         <v>227000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>225000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>204000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>186000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>222000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>217000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>180000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>178000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>218000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>416000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>480000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>485000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>496000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>465000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>456000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>465000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>512000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>509000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>525000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>456000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>494000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>619000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3328000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3264000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3402000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3400000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3362000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3312000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3345000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3220000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="L46" s="3">
-        <v>3043000</v>
       </c>
       <c r="M46" s="3">
         <v>3043000</v>
       </c>
       <c r="N46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="O46" s="3">
         <v>3063000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3010000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2889000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2911000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3244000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3126000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3158000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3177000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3293000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2927000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3374000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3453000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3326,8 +3431,8 @@
       <c r="R47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3350,156 +3455,165 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1227000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1185000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1183000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1145000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1123000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1095000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1054000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1033000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1049000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1033000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1019000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1054000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1083000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1109000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1139000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1234000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1298000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1374000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1451000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1522000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1726000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2378000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E49" s="3">
         <v>315000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>325000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>356000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>384000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>417000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>370000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>404000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>440000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>474000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>506000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>540000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>579000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>619000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>657000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>695000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>734000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>771000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>810000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>841000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>875000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1000000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1353000</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3763,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>213000</v>
+        <v>220000</v>
       </c>
       <c r="E52" s="3">
         <v>213000</v>
       </c>
       <c r="F52" s="3">
+        <v>213000</v>
+      </c>
+      <c r="G52" s="3">
         <v>217000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>192000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>212000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>234000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>189000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>177000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>118000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>138000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>85000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>92000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>93000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>97000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>70000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>66000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>68000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>73000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>79000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>85000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>65000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>109000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5141000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5054000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5159000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5188000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5111000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5090000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5068000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4895000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4648000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4709000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4720000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4707000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4735000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4684000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4774000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5148000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5160000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5295000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5434000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5664000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5409000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6165000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7293000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,452 +4054,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E57" s="3">
         <v>714000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>792000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>723000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>771000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>716000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>679000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>620000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>502000</v>
       </c>
       <c r="L57" s="3">
         <v>502000</v>
       </c>
       <c r="M57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="N57" s="3">
         <v>460000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>425000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>448000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>385000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>380000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>350000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>348000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>330000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>325000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>332000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>384000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>544000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>585000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E58" s="3">
         <v>68000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>61000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>67000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>66000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>148000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>214000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>134000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>75000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>164000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>64000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>211000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>14000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>26000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>13000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E59" s="3">
         <v>536000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>541000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>549000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>561000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>638000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>586000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>592000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>575000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>523000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>965000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>945000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>871000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>902000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>940000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>963000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>885000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1023000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1024000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1070000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1074000</v>
       </c>
       <c r="Y59" s="3">
         <v>1074000</v>
       </c>
       <c r="Z59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1503000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1567000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1696000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1667000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1691000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1800000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1866000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1731000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1464000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1511000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1470000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1384000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1383000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1300000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1332000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1524000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1243000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1364000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1362000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1416000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1426000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1644000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1672000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1674000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1691000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1727000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1749000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1755000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1753000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1846000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1993000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2118000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2197000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2366000</v>
       </c>
       <c r="O61" s="3">
         <v>2366000</v>
       </c>
       <c r="P61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="Q61" s="3">
         <v>2416000</v>
       </c>
       <c r="R61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="S61" s="3">
         <v>2431000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2605000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2602000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2601000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2602000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2148000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2149000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2151000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>443000</v>
+      </c>
+      <c r="E62" s="3">
         <v>434000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>325000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>413000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>422000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>433000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>299000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>405000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>391000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>413000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>496000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>485000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>495000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>542000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>530000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>546000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>553000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>508000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>534000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>523000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>530000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>509000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>554000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3622000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3694000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3876000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3832000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3871000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3990000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4146000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4132000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3976000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4123000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4185000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4254000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4269000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4288000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4302000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4527000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4434000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4508000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4527000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4577000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4142000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4346000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4413000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1311000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1428000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1486000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1579000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-992000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1510000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1352000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1285000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1345000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1228000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1091000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>924000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>742000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>645000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>567000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>535000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>453000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>466000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>396000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>472000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>621000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>726000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>787000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>907000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1087000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1267000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1819000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2880000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E81" s="3">
         <v>76000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>157000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>125000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>112000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>140000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>123000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>72000</v>
       </c>
       <c r="M81" s="3">
         <v>72000</v>
       </c>
       <c r="N81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="O81" s="3">
         <v>28000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-161000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-95000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-78000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-116000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-174000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-581000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-966000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5253000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,82 +5811,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>44000</v>
+        <v>45000</v>
       </c>
       <c r="E83" s="3">
         <v>44000</v>
       </c>
       <c r="F83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="G83" s="3">
         <v>46000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>41000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>48000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>84000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>88000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>90000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>87000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>103000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>112000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>114000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>111000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>116000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>117000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>113000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>157000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>124000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E89" s="3">
         <v>142000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>249000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>262000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>150000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>131000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>375000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>172000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>201000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>84000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>193000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>160000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>60000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>88000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>114000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>46000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>74000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>127000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>31000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6379,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-78000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-62000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-64000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-49000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-54000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-35000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-93000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-79000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-86000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-92000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-54000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-131000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-58000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-32000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-81000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>21000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-75000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6497,8 +6731,8 @@
       <c r="F96" s="3">
         <v>18000</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>11</v>
+      <c r="G96" s="3">
+        <v>18000</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>11</v>
@@ -6515,8 +6749,8 @@
       <c r="L96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,226 +7022,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-133000</v>
+        <v>-97000</v>
       </c>
       <c r="E100" s="3">
         <v>-133000</v>
       </c>
       <c r="F100" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-89000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-102000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-187000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-126000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-91000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-170000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-127000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-159000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-64000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-20000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-338000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-50000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-52000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>412000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-170000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-16000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-21000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-22000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-33000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-33000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>58000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-126000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>117000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-61000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-129000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-57000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-333000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>59000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>58000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>537000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-250000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -656,366 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1289000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1232000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1204000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1193000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1341000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1409000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1405000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1358000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1362000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1313000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1274000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1186000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1209000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1120000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1064000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>938000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>965000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>945000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>903000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>832000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>842000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>807000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>821000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1215000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1246000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>892000</v>
+      </c>
+      <c r="E9" s="3">
         <v>844000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>829000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>819000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>913000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>917000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>891000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>884000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>899000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>859000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>847000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>790000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>807000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>775000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>756000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>682000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>717000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>686000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>677000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>636000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>654000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>631000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>609000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>913000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>953000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E10" s="3">
         <v>388000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>375000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>374000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>428000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>492000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>514000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>474000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>463000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>454000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>427000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>396000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>402000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>345000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>308000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>256000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>248000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>259000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>226000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>196000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>188000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>176000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>212000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>302000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>293000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1044,61 +1056,62 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E12" s="3">
         <v>27000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>31000</v>
       </c>
       <c r="J12" s="3">
         <v>31000</v>
       </c>
       <c r="K12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="L12" s="3">
         <v>29000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>21000</v>
       </c>
       <c r="U12" s="3">
         <v>21000</v>
@@ -1107,25 +1120,28 @@
         <v>21000</v>
       </c>
       <c r="W12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="X12" s="3">
         <v>20000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>23000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>33000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>36000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1204,34 +1220,37 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E14" s="3">
         <v>11000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-59000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>29000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>11</v>
@@ -1242,91 +1261,94 @@
       <c r="N14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P14" s="3">
         <v>9000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-14000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>117000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>51000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-8000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>137000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>31000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>441000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>852000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E15" s="3">
         <v>67000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>64000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>62000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>83000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>89000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>86000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>85000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>83000</v>
       </c>
       <c r="L15" s="3">
         <v>83000</v>
       </c>
       <c r="M15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="N15" s="3">
         <v>81000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>80000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>38000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>39000</v>
       </c>
       <c r="Q15" s="3">
         <v>39000</v>
@@ -1346,8 +1368,8 @@
       <c r="V15" s="3">
         <v>39000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>11</v>
+      <c r="W15" s="3">
+        <v>39000</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>11</v>
@@ -1364,8 +1386,11 @@
       <c r="AB15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1083000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1043000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1026000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1022000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1143000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1166000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1136000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1122000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1146000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1095000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1073000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1001000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1043000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>960000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>920000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1043000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>933000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>878000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>845000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>949000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>867000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1318000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2046000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E18" s="3">
         <v>189000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>178000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>171000</v>
       </c>
-      <c r="G18" s="3">
-        <v>198000</v>
-      </c>
       <c r="H18" s="3">
+        <v>232000</v>
+      </c>
+      <c r="I18" s="3">
         <v>243000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>269000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>236000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>216000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>218000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>201000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>185000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>166000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>119000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>104000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-78000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>25000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-107000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-497000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-831000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5373000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,179 +1613,186 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>16000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>25000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>20000</v>
       </c>
-      <c r="G20" s="3">
-        <v>4000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I20" s="3">
         <v>41000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>30000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>22000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>36000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>24000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>96000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>35000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-69000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-80000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-64000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-59000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-73000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-83000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-74000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-67000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-99000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-83000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E21" s="3">
         <v>240000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>217000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>213000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>320000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>291000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>325000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>299000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>263000</v>
+      </c>
+      <c r="M21" s="3">
         <v>277000</v>
       </c>
-      <c r="H21" s="3">
-        <v>291000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>325000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>299000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>263000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>277000</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>186000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>230000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>181000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>151000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>114000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-34000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>51000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>56000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-58000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-454000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-757000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5456000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E22" s="3">
         <v>34000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>37000</v>
       </c>
       <c r="G22" s="3">
         <v>37000</v>
@@ -1762,25 +1801,25 @@
         <v>37000</v>
       </c>
       <c r="I22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J22" s="3">
         <v>41000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>43000</v>
       </c>
       <c r="K22" s="3">
         <v>43000</v>
       </c>
       <c r="L22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="M22" s="3">
         <v>45000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>47000</v>
       </c>
       <c r="N22" s="3">
         <v>47000</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1821,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E23" s="3">
         <v>139000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>191000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>96000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>169000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>178000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>210000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>182000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>149000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>164000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>74000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>119000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>97000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>63000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-46000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-137000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-61000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-58000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-87000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-174000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-159000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-567000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5332000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>52000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>46000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>45000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>73000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>59000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>38000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>20000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>28000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>23000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>44000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>68000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E26" s="3">
         <v>87000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>145000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>86000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>124000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>166000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>137000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>123000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>147000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>131000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>90000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>81000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>76000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>37000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-74000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-157000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-89000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-73000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-110000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-195000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-167000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-579000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-958000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5264000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E27" s="3">
         <v>81000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>136000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>76000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>112000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>157000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>125000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>112000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>140000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>123000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>82000</v>
-      </c>
-      <c r="N27" s="3">
-        <v>72000</v>
       </c>
       <c r="O27" s="3">
         <v>72000</v>
       </c>
       <c r="P27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Q27" s="3">
         <v>28000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-80000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-161000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-95000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-78000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-116000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-581000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-966000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5253000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2381,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-25000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-20000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-41000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-30000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-22000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-36000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-24000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-96000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-35000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>69000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>56000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>80000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>64000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>59000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>73000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>83000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>74000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>67000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>99000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>70000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>83000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>41000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E33" s="3">
         <v>81000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>136000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>112000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>157000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>125000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>112000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>140000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>123000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>82000</v>
-      </c>
-      <c r="N33" s="3">
-        <v>72000</v>
       </c>
       <c r="O33" s="3">
         <v>72000</v>
       </c>
       <c r="P33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Q33" s="3">
         <v>28000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-80000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-161000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-95000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-78000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-116000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-581000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-966000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5253000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E35" s="3">
         <v>81000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>136000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>112000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>157000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>125000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>112000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>140000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>123000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>82000</v>
-      </c>
-      <c r="N35" s="3">
-        <v>72000</v>
       </c>
       <c r="O35" s="3">
         <v>72000</v>
       </c>
       <c r="P35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Q35" s="3">
         <v>28000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-80000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-161000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-95000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-78000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-116000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-581000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-966000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5253000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,88 +3091,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>987000</v>
+      </c>
+      <c r="E41" s="3">
         <v>967000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>943000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>873000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>916000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>920000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>862000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>824000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>958000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>839000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>787000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>833000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>910000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>933000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>879000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>841000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>951000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1291000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1217000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1177000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1118000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1121000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>680000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>670000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>618000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3166,328 +3255,343 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1305000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1342000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1227000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1218000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1322000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1299000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1372000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1303000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1277000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1318000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1120000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1123000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1028000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>927000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>930000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>868000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>825000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>816000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>782000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>793000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>833000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>836000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>929000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1206000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1244000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>836000</v>
+      </c>
+      <c r="E44" s="3">
         <v>880000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>881000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>889000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>880000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>919000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>884000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>850000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>788000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>776000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>751000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>719000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>689000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>723000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>716000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>684000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>670000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>681000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>662000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>676000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>717000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>811000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>862000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1004000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>972000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E45" s="3">
         <v>223000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>217000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>227000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>225000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>204000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>186000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>222000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>217000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>180000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>178000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>218000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>416000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>480000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>485000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>496000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>465000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>456000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>465000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>512000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>509000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>525000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>456000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>494000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>619000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3372000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3476000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3328000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3264000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3402000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3400000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3362000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3312000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3345000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3220000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="N46" s="3">
-        <v>3043000</v>
       </c>
       <c r="O46" s="3">
         <v>3043000</v>
       </c>
       <c r="P46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="Q46" s="3">
         <v>3063000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3010000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2889000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2911000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3244000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3126000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3158000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3177000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3293000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2927000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3374000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3453000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3542,8 +3646,8 @@
       <c r="T47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3566,168 +3670,177 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1252000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1244000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1260000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1227000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1185000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1183000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1145000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1123000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1095000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1054000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1033000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1049000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1033000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1019000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1054000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1083000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1109000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1139000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1234000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1298000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1374000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1451000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1522000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1726000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2378000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E49" s="3">
         <v>294000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>305000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>315000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>325000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>356000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>384000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>417000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>370000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>404000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>440000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>474000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>506000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>540000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>579000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>619000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>657000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>695000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>734000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>771000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>810000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>841000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>875000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1000000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1353000</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E52" s="3">
         <v>230000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>220000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>213000</v>
       </c>
       <c r="G52" s="3">
         <v>213000</v>
       </c>
       <c r="H52" s="3">
+        <v>213000</v>
+      </c>
+      <c r="I52" s="3">
         <v>217000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>192000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>212000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>234000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>189000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>177000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>118000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>138000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>85000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>92000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>93000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>97000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>70000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>66000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>68000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>73000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>79000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>85000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>65000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>109000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5197000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5272000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5141000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5054000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5159000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5188000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5111000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5090000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5068000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4895000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4648000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4709000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4720000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4707000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4735000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4684000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4774000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5148000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5160000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5295000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5434000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5664000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5409000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6165000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7293000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,488 +4315,507 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>650000</v>
+      </c>
+      <c r="E57" s="3">
         <v>690000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>685000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>714000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>792000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>723000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>771000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>716000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>679000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>620000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>502000</v>
       </c>
       <c r="N57" s="3">
         <v>502000</v>
       </c>
       <c r="O57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="P57" s="3">
         <v>460000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>425000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>448000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>385000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>380000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>350000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>348000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>330000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>325000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>332000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>384000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>544000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>585000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E58" s="3">
         <v>174000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>73000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>68000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>67000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>66000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>148000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>214000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>134000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>75000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>164000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>45000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>64000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>211000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>14000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>26000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>13000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E59" s="3">
         <v>533000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>493000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>536000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>541000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>549000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>561000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>638000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>586000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>592000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>575000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>523000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>965000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>945000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>871000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>902000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>940000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>963000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>885000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1023000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1024000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1070000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1074000</v>
       </c>
       <c r="AA59" s="3">
         <v>1074000</v>
       </c>
       <c r="AB59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="AC59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1537000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1678000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1503000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1567000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1696000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1667000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1691000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1800000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1866000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1731000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1464000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1511000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1470000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1384000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1383000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1300000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1332000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1524000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1243000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1364000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1362000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1416000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1426000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1644000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1672000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1564000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1570000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1674000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1691000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1727000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1749000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1755000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1753000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1846000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1993000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2118000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2197000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2366000</v>
       </c>
       <c r="Q61" s="3">
         <v>2366000</v>
       </c>
       <c r="R61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="S61" s="3">
         <v>2416000</v>
       </c>
       <c r="T61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="U61" s="3">
         <v>2431000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2605000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2602000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2601000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2602000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2148000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2149000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2151000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E62" s="3">
         <v>454000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>443000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>434000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>325000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>413000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>422000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>433000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>299000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>405000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>391000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>413000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>496000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>485000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>495000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>542000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>530000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>546000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>553000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>508000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>534000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>523000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>530000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>509000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>554000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3501000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3705000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3622000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3694000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3876000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3832000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3871000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3990000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4146000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4132000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3976000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4123000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4185000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4254000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4269000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4288000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4302000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4527000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4434000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4508000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4527000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4577000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4142000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4346000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4413000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5256,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1129000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1249000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1311000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1428000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1486000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1579000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-992000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1699000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1560000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1510000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1352000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1285000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1345000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1228000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1091000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>924000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>742000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>645000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>567000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>535000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>453000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>466000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>396000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>472000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>621000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>726000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>787000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>907000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1087000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1267000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1819000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2880000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E81" s="3">
         <v>81000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>136000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>112000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>157000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>125000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>112000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>140000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>123000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>82000</v>
-      </c>
-      <c r="N81" s="3">
-        <v>72000</v>
       </c>
       <c r="O81" s="3">
         <v>72000</v>
       </c>
       <c r="P81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Q81" s="3">
         <v>28000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-80000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-161000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-95000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-78000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-116000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-581000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-966000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5253000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E83" s="3">
         <v>46000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>44000</v>
       </c>
       <c r="G83" s="3">
         <v>44000</v>
       </c>
       <c r="H83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="I83" s="3">
         <v>46000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>41000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>48000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>84000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>88000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>90000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>87000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>103000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>112000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>114000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>111000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>116000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>117000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>113000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>157000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>124000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E89" s="3">
         <v>138000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>128000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>142000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>249000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>262000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>150000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>131000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>375000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>172000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>201000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>84000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>193000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>160000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>60000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-64000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>88000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>114000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>46000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>74000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>22000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>127000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>31000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>30000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-54000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-78000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-62000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-67000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-64000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-49000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-24000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-54000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>43000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-79000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-86000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-92000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-61000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-131000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-58000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-64000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>9000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-81000</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>21000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-51000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-75000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6971,8 +7204,8 @@
       <c r="H96" s="3">
         <v>18000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>11</v>
+      <c r="I96" s="3">
+        <v>18000</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>11</v>
@@ -6989,8 +7222,8 @@
       <c r="N96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7031,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,244 +7513,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-47000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-97000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-133000</v>
       </c>
       <c r="G100" s="3">
         <v>-133000</v>
       </c>
       <c r="H100" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-89000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-102000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-187000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-126000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-91000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-170000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-127000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-159000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-338000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-50000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-9000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-52000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>412000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-170000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-23000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-16000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-21000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-34000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-22000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-33000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>28000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>73000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>58000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-126000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>117000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>24000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-61000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-129000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>53000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-57000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-333000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>59000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>44000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>58000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>537000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-36000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-250000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>432000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>WFRD</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1289000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1232000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1204000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1193000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1341000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1409000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1405000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1358000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1362000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1313000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1274000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1186000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1209000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1120000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1064000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>938000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>965000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>945000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>903000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>832000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>842000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>807000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>821000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1215000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1246000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1314000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E9" s="3">
         <v>892000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>844000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>829000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>819000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>913000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>917000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>891000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>884000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>899000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>859000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>847000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>790000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>807000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>775000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>756000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>682000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>717000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>686000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>677000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>636000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>654000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>631000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>609000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>913000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>953000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1007000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E10" s="3">
         <v>397000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>388000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>375000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>374000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>428000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>492000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>514000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>474000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>463000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>454000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>427000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>396000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>402000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>345000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>308000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>256000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>248000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>259000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>226000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>196000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>188000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>176000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>212000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>302000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>293000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,64 +1070,65 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E12" s="3">
         <v>22000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>28000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>31000</v>
       </c>
       <c r="K12" s="3">
         <v>31000</v>
       </c>
       <c r="L12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="M12" s="3">
         <v>29000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>30000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22000</v>
-      </c>
-      <c r="U12" s="3">
-        <v>21000</v>
       </c>
       <c r="V12" s="3">
         <v>21000</v>
@@ -1123,25 +1137,28 @@
         <v>21000</v>
       </c>
       <c r="X12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Y12" s="3">
         <v>20000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>23000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>33000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>36000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,37 +1240,40 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E14" s="3">
         <v>46000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>11000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-59000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>29000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>11</v>
@@ -1264,94 +1284,97 @@
       <c r="O14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-14000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>39000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>117000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>51000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-8000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>137000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>31000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>441000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>852000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-5346000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>805000</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E15" s="3">
         <v>74000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>67000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>64000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>62000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>83000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>89000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>86000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>85000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>83000</v>
       </c>
       <c r="M15" s="3">
         <v>83000</v>
       </c>
       <c r="N15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="O15" s="3">
         <v>81000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>80000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>38000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>39000</v>
       </c>
       <c r="R15" s="3">
         <v>39000</v>
@@ -1371,8 +1394,8 @@
       <c r="W15" s="3">
         <v>39000</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>11</v>
+      <c r="X15" s="3">
+        <v>39000</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>11</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1016000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1083000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1043000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1026000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1022000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1109000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1166000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1136000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1122000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1146000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1095000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1073000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1001000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1043000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1001000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>960000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>920000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1043000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>933000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>878000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>845000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>949000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>867000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1318000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2046000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>-4127000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2064000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E18" s="3">
         <v>206000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>189000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>178000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>171000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>232000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>243000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>269000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>236000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>216000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>218000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>201000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>185000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>166000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>119000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>104000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-78000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>25000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-107000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-497000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-831000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5373000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-750000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,188 +1647,195 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>25000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>20000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>41000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>30000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>36000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>24000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>96000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-56000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-80000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-64000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-59000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-73000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-83000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-74000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-99000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-83000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-41000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E21" s="3">
         <v>269000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>240000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>217000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>213000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>320000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>291000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>325000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>299000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>263000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>277000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>186000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>230000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>181000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>151000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>114000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-34000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>51000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>56000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-454000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-757000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5456000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-666000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E22" s="3">
         <v>31000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>37000</v>
       </c>
       <c r="H22" s="3">
         <v>37000</v>
@@ -1804,25 +1844,25 @@
         <v>37000</v>
       </c>
       <c r="J22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K22" s="3">
         <v>41000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>43000</v>
       </c>
       <c r="L22" s="3">
         <v>43000</v>
       </c>
       <c r="M22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="N22" s="3">
         <v>45000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>47000</v>
       </c>
       <c r="O22" s="3">
         <v>47000</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E23" s="3">
         <v>128000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>139000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>191000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>96000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>169000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>178000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>210000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>182000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>149000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>164000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>74000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>119000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>97000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>63000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-46000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-137000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-61000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-58000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-87000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-159000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-567000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5332000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-784000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>52000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>46000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>45000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>73000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>59000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>33000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>38000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>26000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>28000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>44000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>68000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E26" s="3">
         <v>139000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>87000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>145000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>86000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>124000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>166000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>137000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>123000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>147000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>131000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>90000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>81000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>76000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-74000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-157000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-89000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-73000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-110000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-195000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-167000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-579000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-958000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5264000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-815000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E27" s="3">
         <v>138000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>81000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>136000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>76000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>112000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>157000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>125000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>112000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>140000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>123000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>82000</v>
-      </c>
-      <c r="O27" s="3">
-        <v>72000</v>
       </c>
       <c r="P27" s="3">
         <v>72000</v>
       </c>
       <c r="Q27" s="3">
+        <v>72000</v>
+      </c>
+      <c r="R27" s="3">
         <v>28000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-80000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-161000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-95000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-78000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-116000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-581000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-966000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5253000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-25000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-20000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-41000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-30000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-36000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-24000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-96000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>69000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>56000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>80000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>64000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>59000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>73000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>83000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>74000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>67000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>99000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>70000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>83000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>41000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E33" s="3">
         <v>138000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>81000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>136000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>76000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>112000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>157000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>125000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>112000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>140000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>123000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>82000</v>
-      </c>
-      <c r="O33" s="3">
-        <v>72000</v>
       </c>
       <c r="P33" s="3">
         <v>72000</v>
       </c>
       <c r="Q33" s="3">
+        <v>72000</v>
+      </c>
+      <c r="R33" s="3">
         <v>28000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-80000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-161000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-95000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-78000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-116000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-581000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-966000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5253000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E35" s="3">
         <v>138000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>81000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>136000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>76000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>112000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>157000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>125000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>112000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>140000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>123000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>82000</v>
-      </c>
-      <c r="O35" s="3">
-        <v>72000</v>
       </c>
       <c r="P35" s="3">
         <v>72000</v>
       </c>
       <c r="Q35" s="3">
+        <v>72000</v>
+      </c>
+      <c r="R35" s="3">
         <v>28000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-80000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-161000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-95000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-78000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-116000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-581000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-966000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5253000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="E41" s="3">
         <v>987000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>967000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>943000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>873000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>916000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>920000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>862000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>824000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>958000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>839000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>787000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>833000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>910000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>933000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>879000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>841000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>951000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1291000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1217000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1177000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1118000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1121000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>680000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>670000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>618000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>676000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,340 +3348,355 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1305000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1342000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1227000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1218000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1322000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1299000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1372000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1303000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1277000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1318000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1120000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1123000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>927000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>930000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>868000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>825000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>816000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>782000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>793000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>833000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>836000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>929000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1206000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1244000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1277000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E44" s="3">
         <v>836000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>880000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>881000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>889000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>880000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>919000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>884000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>850000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>788000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>776000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>751000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>719000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>689000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>723000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>716000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>684000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>670000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>681000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>662000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>676000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>717000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>811000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>862000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1004000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>972000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1126000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E45" s="3">
         <v>189000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>223000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>217000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>227000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>225000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>204000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>186000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>222000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>217000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>180000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>178000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>218000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>416000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>480000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>485000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>496000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>465000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>456000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>465000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>512000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>509000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>525000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>456000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>494000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>619000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>845000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3372000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3476000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3328000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3264000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3402000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3400000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3362000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3312000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3345000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3220000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2971000</v>
-      </c>
-      <c r="O46" s="3">
-        <v>3043000</v>
       </c>
       <c r="P46" s="3">
         <v>3043000</v>
       </c>
       <c r="Q46" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="R46" s="3">
         <v>3063000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3010000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2889000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2911000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3244000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3126000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3158000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3177000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3293000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2927000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3374000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3453000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3924000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3649,8 +3754,8 @@
       <c r="U47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3673,174 +3778,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1249000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1252000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1244000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1260000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1227000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1185000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1183000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1145000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1123000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1095000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1054000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1033000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1049000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1033000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1019000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1054000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1083000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1109000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1139000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1234000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1298000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1374000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1451000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1522000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1726000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2378000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2143000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E49" s="3">
         <v>285000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>294000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>305000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>315000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>325000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>356000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>384000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>417000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>370000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>404000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>440000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>474000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>506000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>540000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>579000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>619000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>657000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>695000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>734000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>771000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>810000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>841000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>875000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1000000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1353000</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E52" s="3">
         <v>256000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>230000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>220000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>213000</v>
       </c>
       <c r="H52" s="3">
         <v>213000</v>
       </c>
       <c r="I52" s="3">
+        <v>213000</v>
+      </c>
+      <c r="J52" s="3">
         <v>217000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>192000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>212000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>234000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>189000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>177000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>118000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>138000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>85000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>92000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>93000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>97000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>70000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>66000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>68000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>73000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>79000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>85000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>65000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>109000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5085000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5197000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5272000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5141000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5054000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5159000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5188000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5111000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5090000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5068000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4895000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4648000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4709000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4720000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4707000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4735000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4684000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4774000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5148000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5160000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5295000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5434000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5664000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5409000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6165000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7293000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6324000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,91 +4446,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>630000</v>
+      </c>
+      <c r="E57" s="3">
         <v>650000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>690000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>685000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>714000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>792000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>723000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>771000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>716000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>679000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>620000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>502000</v>
       </c>
       <c r="O57" s="3">
         <v>502000</v>
       </c>
       <c r="P57" s="3">
+        <v>502000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>460000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>425000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>448000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>385000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>380000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>350000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>348000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>330000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>325000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>332000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>384000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>544000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>585000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4408,414 +4542,429 @@
         <v>78000</v>
       </c>
       <c r="E58" s="3">
+        <v>78000</v>
+      </c>
+      <c r="F58" s="3">
         <v>174000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>73000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>68000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>61000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>67000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>66000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>148000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>214000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>134000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>75000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>164000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>45000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>64000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>211000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>14000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>26000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>13000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1706000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E59" s="3">
         <v>524000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>533000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>493000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>536000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>541000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>549000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>561000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>638000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>586000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>592000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>575000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>523000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>965000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>945000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>871000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>902000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>940000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>963000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>885000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1023000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1024000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1070000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1010000</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>1074000</v>
       </c>
       <c r="AB59" s="3">
         <v>1074000</v>
       </c>
       <c r="AC59" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="AD59" s="3">
         <v>1047000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1418000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1537000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1678000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1503000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1567000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1696000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1667000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1691000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1866000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1731000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1464000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1511000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1470000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1384000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1383000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1300000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1332000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1524000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1243000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1364000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1362000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1416000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1426000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1644000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1672000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3380000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1552000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1564000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1570000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1674000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1691000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1727000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1749000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1755000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1753000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1846000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1993000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2118000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2197000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2203000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2366000</v>
       </c>
       <c r="R61" s="3">
         <v>2366000</v>
       </c>
       <c r="S61" s="3">
-        <v>2416000</v>
+        <v>2366000</v>
       </c>
       <c r="T61" s="3">
         <v>2416000</v>
       </c>
       <c r="U61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="V61" s="3">
         <v>2431000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2605000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2602000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2601000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2602000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2148000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2149000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2151000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>354000</v>
+      </c>
+      <c r="E62" s="3">
         <v>270000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>454000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>443000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>434000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>325000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>413000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>422000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>433000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>299000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>405000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>391000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>413000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>496000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>485000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>495000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>542000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>530000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>546000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>553000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>508000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>534000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>523000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>530000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>509000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>554000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8109000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3326000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3501000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3705000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3622000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3694000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3876000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3832000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3871000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3990000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4146000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4132000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3976000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4123000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4185000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4254000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4269000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4288000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4302000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4527000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4434000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4508000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4527000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4577000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4142000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4346000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4413000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11586000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1041000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1129000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1249000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1311000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1428000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1486000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1579000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1842000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1954000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2217000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2299000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2371000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2443000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2471000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2477000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2397000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2236000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2141000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2063000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1947000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1747000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1573000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-992000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-10289000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1758000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1699000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1560000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1510000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1352000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1285000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1345000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1228000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1091000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>924000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>742000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>645000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>567000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>535000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>453000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>466000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>396000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>472000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>621000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>726000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>787000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>907000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1087000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1267000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1819000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2880000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-5262000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E81" s="3">
         <v>138000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>81000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>136000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>76000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>112000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>157000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>125000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>112000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>140000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>123000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>82000</v>
-      </c>
-      <c r="O81" s="3">
-        <v>72000</v>
       </c>
       <c r="P81" s="3">
         <v>72000</v>
       </c>
       <c r="Q81" s="3">
+        <v>72000</v>
+      </c>
+      <c r="R81" s="3">
         <v>28000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-80000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-161000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-95000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-78000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-116000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-581000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-966000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5253000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-821000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,91 +6407,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E83" s="3">
         <v>50000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>46000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>44000</v>
       </c>
       <c r="H83" s="3">
         <v>44000</v>
       </c>
       <c r="I83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="J83" s="3">
         <v>46000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>49000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>48000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>84000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>88000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>90000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>87000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>103000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>112000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>114000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>111000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>116000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>117000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>113000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>157000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>124000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E89" s="3">
         <v>268000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>138000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>128000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>142000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>249000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>262000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>150000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>131000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>375000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>172000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>201000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>84000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>193000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>160000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>60000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-64000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>88000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>114000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>46000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>74000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>22000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>127000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>31000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>30000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-201000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-44000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-54000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-78000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-62000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-64000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-24000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-54000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-63000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>43000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-79000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-86000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-92000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-61000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-131000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-58000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>9000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-81000</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>1000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>21000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-75000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,13 +7417,14 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E96" s="3">
         <v>18000</v>
@@ -7207,8 +7441,8 @@
       <c r="I96" s="3">
         <v>18000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>11</v>
+      <c r="J96" s="3">
+        <v>18000</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>11</v>
@@ -7225,8 +7459,8 @@
       <c r="O96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +7759,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-197000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-47000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-97000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-133000</v>
       </c>
       <c r="H100" s="3">
         <v>-133000</v>
       </c>
       <c r="I100" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-89000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-102000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-126000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-91000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-170000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-127000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-64000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-20000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-338000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-50000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-52000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>412000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>648000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-33000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-23000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-16000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-21000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-34000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-22000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>73000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-45000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>58000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-126000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>117000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>24000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-61000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-129000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>53000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-57000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-333000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>59000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>44000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>58000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>537000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-250000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>432000</v>
       </c>
     </row>
